--- a/RESULTS/climatenewsfr/climatenewsfr_results.xlsx
+++ b/RESULTS/climatenewsfr/climatenewsfr_results.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evangeliazve/Documents/Papier EMNLP/Dossier Github - supp material/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AEE30BA-047A-354B-BA0B-0510EC921FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA2EF3B-A433-3D48-A5DD-D913DD1E55A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="840" yWindow="5860" windowWidth="29400" windowHeight="17000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="820" windowWidth="29400" windowHeight="17000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ml_metrics_with_ablation" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ml_metrics_with_ablation!$A$1:$T$361</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ml_metrics_with_ablation!$A$1:$T$289</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="35">
   <si>
     <t>horizon</t>
   </si>
@@ -521,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:T361"/>
+  <dimension ref="A1:T289"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="20" width="19" customWidth="1"/>
@@ -18445,4476 +18445,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A290" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B290" s="2">
-        <v>9</v>
-      </c>
-      <c r="C290" s="2">
-        <v>9</v>
-      </c>
-      <c r="D290" s="2">
-        <v>0</v>
-      </c>
-      <c r="E290" s="2">
-        <v>5</v>
-      </c>
-      <c r="F290" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G290" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H290" s="2">
-        <v>78</v>
-      </c>
-      <c r="I290" s="2">
-        <v>11</v>
-      </c>
-      <c r="J290" s="2">
-        <v>67</v>
-      </c>
-      <c r="K290" s="2">
-        <v>0.95</v>
-      </c>
-      <c r="L290" s="2">
-        <v>8.6602540378443851E-2</v>
-      </c>
-      <c r="M290" s="2">
-        <v>1</v>
-      </c>
-      <c r="N290" s="2">
-        <v>0</v>
-      </c>
-      <c r="O290" s="2">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="P290" s="2">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="Q290" s="2">
-        <v>1</v>
-      </c>
-      <c r="R290" s="2">
-        <v>0</v>
-      </c>
-      <c r="S290" s="2">
-        <v>1</v>
-      </c>
-      <c r="T290" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="291" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A291" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B291" s="2">
-        <v>9</v>
-      </c>
-      <c r="C291" s="2">
-        <v>9</v>
-      </c>
-      <c r="D291" s="2">
-        <v>0</v>
-      </c>
-      <c r="E291" s="2">
-        <v>5</v>
-      </c>
-      <c r="F291" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G291" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H291" s="2">
-        <v>78</v>
-      </c>
-      <c r="I291" s="2">
-        <v>11</v>
-      </c>
-      <c r="J291" s="2">
-        <v>67</v>
-      </c>
-      <c r="K291" s="2">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="L291" s="2">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="M291" s="2">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="N291" s="2">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="O291" s="2">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="P291" s="2">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="Q291" s="2">
-        <v>0.32853835978835982</v>
-      </c>
-      <c r="R291" s="2">
-        <v>8.8147376754867696E-2</v>
-      </c>
-      <c r="S291" s="2">
-        <v>0.68368437118437109</v>
-      </c>
-      <c r="T291" s="2">
-        <v>0.1068346360567254</v>
-      </c>
-    </row>
-    <row r="292" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A292" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B292" s="2">
-        <v>9</v>
-      </c>
-      <c r="C292" s="2">
-        <v>9</v>
-      </c>
-      <c r="D292" s="2">
-        <v>0</v>
-      </c>
-      <c r="E292" s="2">
-        <v>5</v>
-      </c>
-      <c r="F292" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G292" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H292" s="2">
-        <v>78</v>
-      </c>
-      <c r="I292" s="2">
-        <v>11</v>
-      </c>
-      <c r="J292" s="2">
-        <v>67</v>
-      </c>
-      <c r="K292" s="2">
-        <v>0.95</v>
-      </c>
-      <c r="L292" s="2">
-        <v>8.6602540378443851E-2</v>
-      </c>
-      <c r="M292" s="2">
-        <v>1</v>
-      </c>
-      <c r="N292" s="2">
-        <v>0</v>
-      </c>
-      <c r="O292" s="2">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="P292" s="2">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="Q292" s="2">
-        <v>1</v>
-      </c>
-      <c r="R292" s="2">
-        <v>0</v>
-      </c>
-      <c r="S292" s="2">
-        <v>1</v>
-      </c>
-      <c r="T292" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A293" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B293" s="2">
-        <v>9</v>
-      </c>
-      <c r="C293" s="2">
-        <v>9</v>
-      </c>
-      <c r="D293" s="2">
-        <v>0</v>
-      </c>
-      <c r="E293" s="2">
-        <v>5</v>
-      </c>
-      <c r="F293" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G293" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H293" s="2">
-        <v>78</v>
-      </c>
-      <c r="I293" s="2">
-        <v>11</v>
-      </c>
-      <c r="J293" s="2">
-        <v>67</v>
-      </c>
-      <c r="K293" s="2">
-        <v>0.95</v>
-      </c>
-      <c r="L293" s="2">
-        <v>8.6602540378443851E-2</v>
-      </c>
-      <c r="M293" s="2">
-        <v>1</v>
-      </c>
-      <c r="N293" s="2">
-        <v>0</v>
-      </c>
-      <c r="O293" s="2">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="P293" s="2">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="Q293" s="2">
-        <v>1</v>
-      </c>
-      <c r="R293" s="2">
-        <v>0</v>
-      </c>
-      <c r="S293" s="2">
-        <v>1</v>
-      </c>
-      <c r="T293" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A294" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B294" s="2">
-        <v>9</v>
-      </c>
-      <c r="C294" s="2">
-        <v>9</v>
-      </c>
-      <c r="D294" s="2">
-        <v>0</v>
-      </c>
-      <c r="E294" s="2">
-        <v>5</v>
-      </c>
-      <c r="F294" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G294" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H294" s="2">
-        <v>78</v>
-      </c>
-      <c r="I294" s="2">
-        <v>11</v>
-      </c>
-      <c r="J294" s="2">
-        <v>67</v>
-      </c>
-      <c r="K294" s="2">
-        <v>0.95</v>
-      </c>
-      <c r="L294" s="2">
-        <v>8.6602540378443851E-2</v>
-      </c>
-      <c r="M294" s="2">
-        <v>1</v>
-      </c>
-      <c r="N294" s="2">
-        <v>0</v>
-      </c>
-      <c r="O294" s="2">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="P294" s="2">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="Q294" s="2">
-        <v>1</v>
-      </c>
-      <c r="R294" s="2">
-        <v>0</v>
-      </c>
-      <c r="S294" s="2">
-        <v>1</v>
-      </c>
-      <c r="T294" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A295" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B295" s="2">
-        <v>9</v>
-      </c>
-      <c r="C295" s="2">
-        <v>9</v>
-      </c>
-      <c r="D295" s="2">
-        <v>0</v>
-      </c>
-      <c r="E295" s="2">
-        <v>5</v>
-      </c>
-      <c r="F295" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G295" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H295" s="2">
-        <v>78</v>
-      </c>
-      <c r="I295" s="2">
-        <v>11</v>
-      </c>
-      <c r="J295" s="2">
-        <v>67</v>
-      </c>
-      <c r="K295" s="2">
-        <v>0.46785714285714292</v>
-      </c>
-      <c r="L295" s="2">
-        <v>0.29196292048610473</v>
-      </c>
-      <c r="M295" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="N295" s="2">
-        <v>0.35355339059327379</v>
-      </c>
-      <c r="O295" s="2">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="P295" s="2">
-        <v>0.27322660517925001</v>
-      </c>
-      <c r="Q295" s="2">
-        <v>0.39340277777777782</v>
-      </c>
-      <c r="R295" s="2">
-        <v>0.2025311832986055</v>
-      </c>
-      <c r="S295" s="2">
-        <v>0.68898809523809512</v>
-      </c>
-      <c r="T295" s="2">
-        <v>0.11996484450551979</v>
-      </c>
-    </row>
-    <row r="296" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A296" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B296" s="2">
-        <v>9</v>
-      </c>
-      <c r="C296" s="2">
-        <v>9</v>
-      </c>
-      <c r="D296" s="2">
-        <v>0</v>
-      </c>
-      <c r="E296" s="2">
-        <v>5</v>
-      </c>
-      <c r="F296" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G296" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H296" s="2">
-        <v>78</v>
-      </c>
-      <c r="I296" s="2">
-        <v>11</v>
-      </c>
-      <c r="J296" s="2">
-        <v>67</v>
-      </c>
-      <c r="K296" s="2">
-        <v>0</v>
-      </c>
-      <c r="L296" s="2">
-        <v>0</v>
-      </c>
-      <c r="M296" s="2">
-        <v>0</v>
-      </c>
-      <c r="N296" s="2">
-        <v>0</v>
-      </c>
-      <c r="O296" s="2">
-        <v>0</v>
-      </c>
-      <c r="P296" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q296" s="2">
-        <v>0.29771201021201021</v>
-      </c>
-      <c r="R296" s="2">
-        <v>9.3269238633410217E-2</v>
-      </c>
-      <c r="S296" s="2">
-        <v>0.60645604395604391</v>
-      </c>
-      <c r="T296" s="2">
-        <v>0.13292018866004571</v>
-      </c>
-    </row>
-    <row r="297" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A297" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B297" s="2">
-        <v>9</v>
-      </c>
-      <c r="C297" s="2">
-        <v>9</v>
-      </c>
-      <c r="D297" s="2">
-        <v>0</v>
-      </c>
-      <c r="E297" s="2">
-        <v>5</v>
-      </c>
-      <c r="F297" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G297" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H297" s="2">
-        <v>78</v>
-      </c>
-      <c r="I297" s="2">
-        <v>11</v>
-      </c>
-      <c r="J297" s="2">
-        <v>67</v>
-      </c>
-      <c r="K297" s="2">
-        <v>0.91428571428571426</v>
-      </c>
-      <c r="L297" s="2">
-        <v>8.8063057185271076E-2</v>
-      </c>
-      <c r="M297" s="2">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N297" s="2">
-        <v>0.14877975892797601</v>
-      </c>
-      <c r="O297" s="2">
-        <v>1</v>
-      </c>
-      <c r="P297" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q297" s="2">
-        <v>1</v>
-      </c>
-      <c r="R297" s="2">
-        <v>0</v>
-      </c>
-      <c r="S297" s="2">
-        <v>1</v>
-      </c>
-      <c r="T297" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A298" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B298" s="2">
-        <v>9</v>
-      </c>
-      <c r="C298" s="2">
-        <v>9</v>
-      </c>
-      <c r="D298" s="2">
-        <v>0</v>
-      </c>
-      <c r="E298" s="2">
-        <v>5</v>
-      </c>
-      <c r="F298" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G298" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H298" s="2">
-        <v>78</v>
-      </c>
-      <c r="I298" s="2">
-        <v>11</v>
-      </c>
-      <c r="J298" s="2">
-        <v>67</v>
-      </c>
-      <c r="K298" s="2">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="L298" s="2">
-        <v>0.1020620726159658</v>
-      </c>
-      <c r="M298" s="2">
-        <v>0.27500000000000002</v>
-      </c>
-      <c r="N298" s="2">
-        <v>9.5379359518829976E-2</v>
-      </c>
-      <c r="O298" s="2">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="P298" s="2">
-        <v>0.13819269959814159</v>
-      </c>
-      <c r="Q298" s="2">
-        <v>0.51884920634920628</v>
-      </c>
-      <c r="R298" s="2">
-        <v>0.12413485568553879</v>
-      </c>
-      <c r="S298" s="2">
-        <v>0.78548534798534808</v>
-      </c>
-      <c r="T298" s="2">
-        <v>4.584417285911032E-2</v>
-      </c>
-    </row>
-    <row r="299" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A299" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B299" s="2">
-        <v>9</v>
-      </c>
-      <c r="C299" s="2">
-        <v>9</v>
-      </c>
-      <c r="D299" s="2">
-        <v>0</v>
-      </c>
-      <c r="E299" s="2">
-        <v>5</v>
-      </c>
-      <c r="F299" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G299" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H299" s="2">
-        <v>78</v>
-      </c>
-      <c r="I299" s="2">
-        <v>11</v>
-      </c>
-      <c r="J299" s="2">
-        <v>67</v>
-      </c>
-      <c r="K299" s="2">
-        <v>0.91428571428571426</v>
-      </c>
-      <c r="L299" s="2">
-        <v>8.8063057185271076E-2</v>
-      </c>
-      <c r="M299" s="2">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N299" s="2">
-        <v>0.14877975892797601</v>
-      </c>
-      <c r="O299" s="2">
-        <v>1</v>
-      </c>
-      <c r="P299" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q299" s="2">
-        <v>1</v>
-      </c>
-      <c r="R299" s="2">
-        <v>0</v>
-      </c>
-      <c r="S299" s="2">
-        <v>1</v>
-      </c>
-      <c r="T299" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A300" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B300" s="2">
-        <v>9</v>
-      </c>
-      <c r="C300" s="2">
-        <v>9</v>
-      </c>
-      <c r="D300" s="2">
-        <v>0</v>
-      </c>
-      <c r="E300" s="2">
-        <v>5</v>
-      </c>
-      <c r="F300" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G300" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H300" s="2">
-        <v>78</v>
-      </c>
-      <c r="I300" s="2">
-        <v>11</v>
-      </c>
-      <c r="J300" s="2">
-        <v>67</v>
-      </c>
-      <c r="K300" s="2">
-        <v>0.91428571428571426</v>
-      </c>
-      <c r="L300" s="2">
-        <v>8.8063057185271076E-2</v>
-      </c>
-      <c r="M300" s="2">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N300" s="2">
-        <v>0.14877975892797601</v>
-      </c>
-      <c r="O300" s="2">
-        <v>1</v>
-      </c>
-      <c r="P300" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q300" s="2">
-        <v>1</v>
-      </c>
-      <c r="R300" s="2">
-        <v>0</v>
-      </c>
-      <c r="S300" s="2">
-        <v>1</v>
-      </c>
-      <c r="T300" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A301" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B301" s="2">
-        <v>9</v>
-      </c>
-      <c r="C301" s="2">
-        <v>9</v>
-      </c>
-      <c r="D301" s="2">
-        <v>0</v>
-      </c>
-      <c r="E301" s="2">
-        <v>5</v>
-      </c>
-      <c r="F301" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G301" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H301" s="2">
-        <v>78</v>
-      </c>
-      <c r="I301" s="2">
-        <v>11</v>
-      </c>
-      <c r="J301" s="2">
-        <v>67</v>
-      </c>
-      <c r="K301" s="2">
-        <v>0.91428571428571426</v>
-      </c>
-      <c r="L301" s="2">
-        <v>8.8063057185271076E-2</v>
-      </c>
-      <c r="M301" s="2">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N301" s="2">
-        <v>0.14877975892797601</v>
-      </c>
-      <c r="O301" s="2">
-        <v>1</v>
-      </c>
-      <c r="P301" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q301" s="2">
-        <v>1</v>
-      </c>
-      <c r="R301" s="2">
-        <v>0</v>
-      </c>
-      <c r="S301" s="2">
-        <v>1</v>
-      </c>
-      <c r="T301" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A302" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B302" s="2">
-        <v>9</v>
-      </c>
-      <c r="C302" s="2">
-        <v>9</v>
-      </c>
-      <c r="D302" s="2">
-        <v>0</v>
-      </c>
-      <c r="E302" s="2">
-        <v>5</v>
-      </c>
-      <c r="F302" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G302" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H302" s="2">
-        <v>78</v>
-      </c>
-      <c r="I302" s="2">
-        <v>11</v>
-      </c>
-      <c r="J302" s="2">
-        <v>67</v>
-      </c>
-      <c r="K302" s="2">
-        <v>0</v>
-      </c>
-      <c r="L302" s="2">
-        <v>0</v>
-      </c>
-      <c r="M302" s="2">
-        <v>0</v>
-      </c>
-      <c r="N302" s="2">
-        <v>0</v>
-      </c>
-      <c r="O302" s="2">
-        <v>0</v>
-      </c>
-      <c r="P302" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q302" s="2">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="R302" s="2">
-        <v>2.9315098498896439E-2</v>
-      </c>
-      <c r="S302" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T302" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A303" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B303" s="2">
-        <v>9</v>
-      </c>
-      <c r="C303" s="2">
-        <v>9</v>
-      </c>
-      <c r="D303" s="2">
-        <v>0</v>
-      </c>
-      <c r="E303" s="2">
-        <v>5</v>
-      </c>
-      <c r="F303" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G303" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H303" s="2">
-        <v>78</v>
-      </c>
-      <c r="I303" s="2">
-        <v>11</v>
-      </c>
-      <c r="J303" s="2">
-        <v>67</v>
-      </c>
-      <c r="K303" s="2">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="L303" s="2">
-        <v>0.1020620726159658</v>
-      </c>
-      <c r="M303" s="2">
-        <v>0.27500000000000002</v>
-      </c>
-      <c r="N303" s="2">
-        <v>9.5379359518829976E-2</v>
-      </c>
-      <c r="O303" s="2">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="P303" s="2">
-        <v>0.13819269959814159</v>
-      </c>
-      <c r="Q303" s="2">
-        <v>0.54662698412698407</v>
-      </c>
-      <c r="R303" s="2">
-        <v>0.19066469260536631</v>
-      </c>
-      <c r="S303" s="2">
-        <v>0.79296398046398042</v>
-      </c>
-      <c r="T303" s="2">
-        <v>7.1949243665153442E-2</v>
-      </c>
-    </row>
-    <row r="304" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A304" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B304" s="2">
-        <v>9</v>
-      </c>
-      <c r="C304" s="2">
-        <v>9</v>
-      </c>
-      <c r="D304" s="2">
-        <v>0</v>
-      </c>
-      <c r="E304" s="2">
-        <v>5</v>
-      </c>
-      <c r="F304" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G304" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H304" s="2">
-        <v>78</v>
-      </c>
-      <c r="I304" s="2">
-        <v>11</v>
-      </c>
-      <c r="J304" s="2">
-        <v>67</v>
-      </c>
-      <c r="K304" s="2">
-        <v>0.91428571428571426</v>
-      </c>
-      <c r="L304" s="2">
-        <v>8.8063057185271076E-2</v>
-      </c>
-      <c r="M304" s="2">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N304" s="2">
-        <v>0.14877975892797601</v>
-      </c>
-      <c r="O304" s="2">
-        <v>1</v>
-      </c>
-      <c r="P304" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q304" s="2">
-        <v>1</v>
-      </c>
-      <c r="R304" s="2">
-        <v>0</v>
-      </c>
-      <c r="S304" s="2">
-        <v>1</v>
-      </c>
-      <c r="T304" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A305" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B305" s="2">
-        <v>9</v>
-      </c>
-      <c r="C305" s="2">
-        <v>9</v>
-      </c>
-      <c r="D305" s="2">
-        <v>0</v>
-      </c>
-      <c r="E305" s="2">
-        <v>5</v>
-      </c>
-      <c r="F305" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G305" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H305" s="2">
-        <v>78</v>
-      </c>
-      <c r="I305" s="2">
-        <v>11</v>
-      </c>
-      <c r="J305" s="2">
-        <v>67</v>
-      </c>
-      <c r="K305" s="2">
-        <v>0.18333333333333329</v>
-      </c>
-      <c r="L305" s="2">
-        <v>0.18484227510682361</v>
-      </c>
-      <c r="M305" s="2">
-        <v>0.16666666666666671</v>
-      </c>
-      <c r="N305" s="2">
-        <v>0.16666666666666671</v>
-      </c>
-      <c r="O305" s="2">
-        <v>0.20833333333333329</v>
-      </c>
-      <c r="P305" s="2">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="Q305" s="2">
-        <v>0.3105387667887668</v>
-      </c>
-      <c r="R305" s="2">
-        <v>0.14747677528381031</v>
-      </c>
-      <c r="S305" s="2">
-        <v>0.43162393162393159</v>
-      </c>
-      <c r="T305" s="2">
-        <v>8.9896085333173614E-2</v>
-      </c>
-    </row>
-    <row r="306" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A306" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B306" s="2">
-        <v>9</v>
-      </c>
-      <c r="C306" s="2">
-        <v>9</v>
-      </c>
-      <c r="D306" s="2">
-        <v>0</v>
-      </c>
-      <c r="E306" s="2">
-        <v>5</v>
-      </c>
-      <c r="F306" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G306" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H306" s="2">
-        <v>78</v>
-      </c>
-      <c r="I306" s="2">
-        <v>11</v>
-      </c>
-      <c r="J306" s="2">
-        <v>67</v>
-      </c>
-      <c r="K306" s="2">
-        <v>1</v>
-      </c>
-      <c r="L306" s="2">
-        <v>0</v>
-      </c>
-      <c r="M306" s="2">
-        <v>1</v>
-      </c>
-      <c r="N306" s="2">
-        <v>0</v>
-      </c>
-      <c r="O306" s="2">
-        <v>1</v>
-      </c>
-      <c r="P306" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q306" s="2">
-        <v>1</v>
-      </c>
-      <c r="R306" s="2">
-        <v>0</v>
-      </c>
-      <c r="S306" s="2">
-        <v>1</v>
-      </c>
-      <c r="T306" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="307" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A307" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B307" s="2">
-        <v>9</v>
-      </c>
-      <c r="C307" s="2">
-        <v>9</v>
-      </c>
-      <c r="D307" s="2">
-        <v>0</v>
-      </c>
-      <c r="E307" s="2">
-        <v>5</v>
-      </c>
-      <c r="F307" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G307" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H307" s="2">
-        <v>78</v>
-      </c>
-      <c r="I307" s="2">
-        <v>11</v>
-      </c>
-      <c r="J307" s="2">
-        <v>67</v>
-      </c>
-      <c r="K307" s="2">
-        <v>0.95</v>
-      </c>
-      <c r="L307" s="2">
-        <v>8.6602540378443851E-2</v>
-      </c>
-      <c r="M307" s="2">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="N307" s="2">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="O307" s="2">
-        <v>1</v>
-      </c>
-      <c r="P307" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q307" s="2">
-        <v>1</v>
-      </c>
-      <c r="R307" s="2">
-        <v>0</v>
-      </c>
-      <c r="S307" s="2">
-        <v>1</v>
-      </c>
-      <c r="T307" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="308" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A308" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B308" s="2">
-        <v>9</v>
-      </c>
-      <c r="C308" s="2">
-        <v>9</v>
-      </c>
-      <c r="D308" s="2">
-        <v>0</v>
-      </c>
-      <c r="E308" s="2">
-        <v>5</v>
-      </c>
-      <c r="F308" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G308" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H308" s="2">
-        <v>78</v>
-      </c>
-      <c r="I308" s="2">
-        <v>11</v>
-      </c>
-      <c r="J308" s="2">
-        <v>67</v>
-      </c>
-      <c r="K308" s="2">
-        <v>1</v>
-      </c>
-      <c r="L308" s="2">
-        <v>0</v>
-      </c>
-      <c r="M308" s="2">
-        <v>1</v>
-      </c>
-      <c r="N308" s="2">
-        <v>0</v>
-      </c>
-      <c r="O308" s="2">
-        <v>1</v>
-      </c>
-      <c r="P308" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q308" s="2">
-        <v>1</v>
-      </c>
-      <c r="R308" s="2">
-        <v>0</v>
-      </c>
-      <c r="S308" s="2">
-        <v>1</v>
-      </c>
-      <c r="T308" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A309" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B309" s="2">
-        <v>9</v>
-      </c>
-      <c r="C309" s="2">
-        <v>9</v>
-      </c>
-      <c r="D309" s="2">
-        <v>0</v>
-      </c>
-      <c r="E309" s="2">
-        <v>5</v>
-      </c>
-      <c r="F309" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G309" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H309" s="2">
-        <v>78</v>
-      </c>
-      <c r="I309" s="2">
-        <v>11</v>
-      </c>
-      <c r="J309" s="2">
-        <v>67</v>
-      </c>
-      <c r="K309" s="2">
-        <v>0.20833333333333329</v>
-      </c>
-      <c r="L309" s="2">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="M309" s="2">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="N309" s="2">
-        <v>0.40824829046386302</v>
-      </c>
-      <c r="O309" s="2">
-        <v>0.16666666666666671</v>
-      </c>
-      <c r="P309" s="2">
-        <v>0.16666666666666671</v>
-      </c>
-      <c r="Q309" s="2">
-        <v>0.23784722222222221</v>
-      </c>
-      <c r="R309" s="2">
-        <v>0.12566358059016541</v>
-      </c>
-      <c r="S309" s="2">
-        <v>0.42113095238095238</v>
-      </c>
-      <c r="T309" s="2">
-        <v>9.4806966882121882E-2</v>
-      </c>
-    </row>
-    <row r="310" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A310" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B310" s="2">
-        <v>9</v>
-      </c>
-      <c r="C310" s="2">
-        <v>9</v>
-      </c>
-      <c r="D310" s="2">
-        <v>0</v>
-      </c>
-      <c r="E310" s="2">
-        <v>5</v>
-      </c>
-      <c r="F310" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G310" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H310" s="2">
-        <v>78</v>
-      </c>
-      <c r="I310" s="2">
-        <v>11</v>
-      </c>
-      <c r="J310" s="2">
-        <v>67</v>
-      </c>
-      <c r="K310" s="2">
-        <v>0.3214285714285714</v>
-      </c>
-      <c r="L310" s="2">
-        <v>0.1041241409793804</v>
-      </c>
-      <c r="M310" s="2">
-        <v>0.24583333333333329</v>
-      </c>
-      <c r="N310" s="2">
-        <v>5.4486236794258409E-2</v>
-      </c>
-      <c r="O310" s="2">
-        <v>0.49999999999999989</v>
-      </c>
-      <c r="P310" s="2">
-        <v>0.28867513459481292</v>
-      </c>
-      <c r="Q310" s="2">
-        <v>0.46755952380952381</v>
-      </c>
-      <c r="R310" s="2">
-        <v>0.30954140861139201</v>
-      </c>
-      <c r="S310" s="2">
-        <v>0.64476495726495719</v>
-      </c>
-      <c r="T310" s="2">
-        <v>0.22805450049045589</v>
-      </c>
-    </row>
-    <row r="311" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A311" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B311" s="2">
-        <v>9</v>
-      </c>
-      <c r="C311" s="2">
-        <v>9</v>
-      </c>
-      <c r="D311" s="2">
-        <v>0</v>
-      </c>
-      <c r="E311" s="2">
-        <v>5</v>
-      </c>
-      <c r="F311" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G311" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H311" s="2">
-        <v>78</v>
-      </c>
-      <c r="I311" s="2">
-        <v>11</v>
-      </c>
-      <c r="J311" s="2">
-        <v>67</v>
-      </c>
-      <c r="K311" s="2">
-        <v>0.95</v>
-      </c>
-      <c r="L311" s="2">
-        <v>8.6602540378443851E-2</v>
-      </c>
-      <c r="M311" s="2">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="N311" s="2">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="O311" s="2">
-        <v>1</v>
-      </c>
-      <c r="P311" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q311" s="2">
-        <v>1</v>
-      </c>
-      <c r="R311" s="2">
-        <v>0</v>
-      </c>
-      <c r="S311" s="2">
-        <v>1</v>
-      </c>
-      <c r="T311" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="312" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A312" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B312" s="2">
-        <v>9</v>
-      </c>
-      <c r="C312" s="2">
-        <v>9</v>
-      </c>
-      <c r="D312" s="2">
-        <v>0</v>
-      </c>
-      <c r="E312" s="2">
-        <v>5</v>
-      </c>
-      <c r="F312" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G312" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H312" s="2">
-        <v>78</v>
-      </c>
-      <c r="I312" s="2">
-        <v>11</v>
-      </c>
-      <c r="J312" s="2">
-        <v>67</v>
-      </c>
-      <c r="K312" s="2">
-        <v>0.16666666666666671</v>
-      </c>
-      <c r="L312" s="2">
-        <v>0.28867513459481292</v>
-      </c>
-      <c r="M312" s="2">
-        <v>0.125</v>
-      </c>
-      <c r="N312" s="2">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="O312" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="P312" s="2">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="Q312" s="2">
-        <v>0.39409305971805969</v>
-      </c>
-      <c r="R312" s="2">
-        <v>0.34986908021491508</v>
-      </c>
-      <c r="S312" s="2">
-        <v>0.49252136752136749</v>
-      </c>
-      <c r="T312" s="2">
-        <v>0.29445925247767801</v>
-      </c>
-    </row>
-    <row r="313" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A313" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B313" s="2">
-        <v>9</v>
-      </c>
-      <c r="C313" s="2">
-        <v>9</v>
-      </c>
-      <c r="D313" s="2">
-        <v>0</v>
-      </c>
-      <c r="E313" s="2">
-        <v>5</v>
-      </c>
-      <c r="F313" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G313" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H313" s="2">
-        <v>78</v>
-      </c>
-      <c r="I313" s="2">
-        <v>11</v>
-      </c>
-      <c r="J313" s="2">
-        <v>67</v>
-      </c>
-      <c r="K313" s="2">
-        <v>1</v>
-      </c>
-      <c r="L313" s="2">
-        <v>0</v>
-      </c>
-      <c r="M313" s="2">
-        <v>1</v>
-      </c>
-      <c r="N313" s="2">
-        <v>0</v>
-      </c>
-      <c r="O313" s="2">
-        <v>1</v>
-      </c>
-      <c r="P313" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q313" s="2">
-        <v>1</v>
-      </c>
-      <c r="R313" s="2">
-        <v>0</v>
-      </c>
-      <c r="S313" s="2">
-        <v>1</v>
-      </c>
-      <c r="T313" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="314" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A314" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B314" s="2">
-        <v>9</v>
-      </c>
-      <c r="C314" s="2">
-        <v>9</v>
-      </c>
-      <c r="D314" s="2">
-        <v>0</v>
-      </c>
-      <c r="E314" s="2">
-        <v>5</v>
-      </c>
-      <c r="F314" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G314" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H314" s="2">
-        <v>78</v>
-      </c>
-      <c r="I314" s="2">
-        <v>11</v>
-      </c>
-      <c r="J314" s="2">
-        <v>67</v>
-      </c>
-      <c r="K314" s="2">
-        <v>0.95</v>
-      </c>
-      <c r="L314" s="2">
-        <v>8.6602540378443851E-2</v>
-      </c>
-      <c r="M314" s="2">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="N314" s="2">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="O314" s="2">
-        <v>1</v>
-      </c>
-      <c r="P314" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q314" s="2">
-        <v>0.95833333333333326</v>
-      </c>
-      <c r="R314" s="2">
-        <v>7.2168783648703258E-2</v>
-      </c>
-      <c r="S314" s="2">
-        <v>0.9910714285714286</v>
-      </c>
-      <c r="T314" s="2">
-        <v>1.546473935329354E-2</v>
-      </c>
-    </row>
-    <row r="315" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A315" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B315" s="2">
-        <v>9</v>
-      </c>
-      <c r="C315" s="2">
-        <v>9</v>
-      </c>
-      <c r="D315" s="2">
-        <v>0</v>
-      </c>
-      <c r="E315" s="2">
-        <v>5</v>
-      </c>
-      <c r="F315" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G315" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H315" s="2">
-        <v>78</v>
-      </c>
-      <c r="I315" s="2">
-        <v>11</v>
-      </c>
-      <c r="J315" s="2">
-        <v>67</v>
-      </c>
-      <c r="K315" s="2">
-        <v>1</v>
-      </c>
-      <c r="L315" s="2">
-        <v>0</v>
-      </c>
-      <c r="M315" s="2">
-        <v>1</v>
-      </c>
-      <c r="N315" s="2">
-        <v>0</v>
-      </c>
-      <c r="O315" s="2">
-        <v>1</v>
-      </c>
-      <c r="P315" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q315" s="2">
-        <v>1</v>
-      </c>
-      <c r="R315" s="2">
-        <v>0</v>
-      </c>
-      <c r="S315" s="2">
-        <v>1</v>
-      </c>
-      <c r="T315" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="316" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A316" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B316" s="2">
-        <v>9</v>
-      </c>
-      <c r="C316" s="2">
-        <v>9</v>
-      </c>
-      <c r="D316" s="2">
-        <v>0</v>
-      </c>
-      <c r="E316" s="2">
-        <v>5</v>
-      </c>
-      <c r="F316" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G316" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H316" s="2">
-        <v>78</v>
-      </c>
-      <c r="I316" s="2">
-        <v>11</v>
-      </c>
-      <c r="J316" s="2">
-        <v>67</v>
-      </c>
-      <c r="K316" s="2">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="L316" s="2">
-        <v>0.14433756729740641</v>
-      </c>
-      <c r="M316" s="2">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="N316" s="2">
-        <v>0.14433756729740641</v>
-      </c>
-      <c r="O316" s="2">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="P316" s="2">
-        <v>0.14433756729740641</v>
-      </c>
-      <c r="Q316" s="2">
-        <v>0.17539682539682541</v>
-      </c>
-      <c r="R316" s="2">
-        <v>6.8214303027782516E-2</v>
-      </c>
-      <c r="S316" s="2">
-        <v>0.35367063492063489</v>
-      </c>
-      <c r="T316" s="2">
-        <v>0.12954978020007071</v>
-      </c>
-    </row>
-    <row r="317" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A317" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B317" s="2">
-        <v>9</v>
-      </c>
-      <c r="C317" s="2">
-        <v>9</v>
-      </c>
-      <c r="D317" s="2">
-        <v>0</v>
-      </c>
-      <c r="E317" s="2">
-        <v>5</v>
-      </c>
-      <c r="F317" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G317" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H317" s="2">
-        <v>78</v>
-      </c>
-      <c r="I317" s="2">
-        <v>11</v>
-      </c>
-      <c r="J317" s="2">
-        <v>67</v>
-      </c>
-      <c r="K317" s="2">
-        <v>0.35119047619047622</v>
-      </c>
-      <c r="L317" s="2">
-        <v>8.8087193969932989E-2</v>
-      </c>
-      <c r="M317" s="2">
-        <v>0.29166666666666657</v>
-      </c>
-      <c r="N317" s="2">
-        <v>4.1666666666666657E-2</v>
-      </c>
-      <c r="O317" s="2">
-        <v>0.49999999999999989</v>
-      </c>
-      <c r="P317" s="2">
-        <v>0.28867513459481292</v>
-      </c>
-      <c r="Q317" s="2">
-        <v>0.44231913919413912</v>
-      </c>
-      <c r="R317" s="2">
-        <v>0.32277170080521272</v>
-      </c>
-      <c r="S317" s="2">
-        <v>0.55822649572649574</v>
-      </c>
-      <c r="T317" s="2">
-        <v>0.26692034952258969</v>
-      </c>
-    </row>
-    <row r="318" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A318" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B318" s="2">
-        <v>9</v>
-      </c>
-      <c r="C318" s="2">
-        <v>9</v>
-      </c>
-      <c r="D318" s="2">
-        <v>0</v>
-      </c>
-      <c r="E318" s="2">
-        <v>5</v>
-      </c>
-      <c r="F318" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G318" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H318" s="2">
-        <v>78</v>
-      </c>
-      <c r="I318" s="2">
-        <v>11</v>
-      </c>
-      <c r="J318" s="2">
-        <v>67</v>
-      </c>
-      <c r="K318" s="2">
-        <v>0.9642857142857143</v>
-      </c>
-      <c r="L318" s="2">
-        <v>6.1858957413174209E-2</v>
-      </c>
-      <c r="M318" s="2">
-        <v>0.9375</v>
-      </c>
-      <c r="N318" s="2">
-        <v>0.1082531754730548</v>
-      </c>
-      <c r="O318" s="2">
-        <v>1</v>
-      </c>
-      <c r="P318" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q318" s="2">
-        <v>0.9375</v>
-      </c>
-      <c r="R318" s="2">
-        <v>0.1082531754730548</v>
-      </c>
-      <c r="S318" s="2">
-        <v>0.99038461538461542</v>
-      </c>
-      <c r="T318" s="2">
-        <v>1.665433468816227E-2</v>
-      </c>
-    </row>
-    <row r="319" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A319" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B319" s="2">
-        <v>9</v>
-      </c>
-      <c r="C319" s="2">
-        <v>9</v>
-      </c>
-      <c r="D319" s="2">
-        <v>0</v>
-      </c>
-      <c r="E319" s="2">
-        <v>5</v>
-      </c>
-      <c r="F319" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G319" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H319" s="2">
-        <v>78</v>
-      </c>
-      <c r="I319" s="2">
-        <v>11</v>
-      </c>
-      <c r="J319" s="2">
-        <v>67</v>
-      </c>
-      <c r="K319" s="2">
-        <v>0.28749999999999998</v>
-      </c>
-      <c r="L319" s="2">
-        <v>0.18833148966649199</v>
-      </c>
-      <c r="M319" s="2">
-        <v>0.21309523809523809</v>
-      </c>
-      <c r="N319" s="2">
-        <v>0.14813179000769669</v>
-      </c>
-      <c r="O319" s="2">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="P319" s="2">
-        <v>0.27322660517925001</v>
-      </c>
-      <c r="Q319" s="2">
-        <v>0.31200396825396831</v>
-      </c>
-      <c r="R319" s="2">
-        <v>7.5616911966063835E-2</v>
-      </c>
-      <c r="S319" s="2">
-        <v>0.7123397435897435</v>
-      </c>
-      <c r="T319" s="2">
-        <v>7.0380667244831843E-2</v>
-      </c>
-    </row>
-    <row r="320" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A320" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B320" s="2">
-        <v>9</v>
-      </c>
-      <c r="C320" s="2">
-        <v>9</v>
-      </c>
-      <c r="D320" s="2">
-        <v>0</v>
-      </c>
-      <c r="E320" s="2">
-        <v>5</v>
-      </c>
-      <c r="F320" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G320" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H320" s="2">
-        <v>78</v>
-      </c>
-      <c r="I320" s="2">
-        <v>11</v>
-      </c>
-      <c r="J320" s="2">
-        <v>67</v>
-      </c>
-      <c r="K320" s="2">
-        <v>1</v>
-      </c>
-      <c r="L320" s="2">
-        <v>0</v>
-      </c>
-      <c r="M320" s="2">
-        <v>1</v>
-      </c>
-      <c r="N320" s="2">
-        <v>0</v>
-      </c>
-      <c r="O320" s="2">
-        <v>1</v>
-      </c>
-      <c r="P320" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q320" s="2">
-        <v>1</v>
-      </c>
-      <c r="R320" s="2">
-        <v>0</v>
-      </c>
-      <c r="S320" s="2">
-        <v>1</v>
-      </c>
-      <c r="T320" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="321" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A321" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B321" s="2">
-        <v>9</v>
-      </c>
-      <c r="C321" s="2">
-        <v>9</v>
-      </c>
-      <c r="D321" s="2">
-        <v>0</v>
-      </c>
-      <c r="E321" s="2">
-        <v>5</v>
-      </c>
-      <c r="F321" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G321" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H321" s="2">
-        <v>78</v>
-      </c>
-      <c r="I321" s="2">
-        <v>11</v>
-      </c>
-      <c r="J321" s="2">
-        <v>67</v>
-      </c>
-      <c r="K321" s="2">
-        <v>0.9375</v>
-      </c>
-      <c r="L321" s="2">
-        <v>0.1082531754730548</v>
-      </c>
-      <c r="M321" s="2">
-        <v>0.9</v>
-      </c>
-      <c r="N321" s="2">
-        <v>0.1732050807568877</v>
-      </c>
-      <c r="O321" s="2">
-        <v>1</v>
-      </c>
-      <c r="P321" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q321" s="2">
-        <v>0.9</v>
-      </c>
-      <c r="R321" s="2">
-        <v>0.1732050807568877</v>
-      </c>
-      <c r="S321" s="2">
-        <v>0.98076923076923084</v>
-      </c>
-      <c r="T321" s="2">
-        <v>3.330866937632454E-2</v>
-      </c>
-    </row>
-    <row r="322" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A322" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B322" s="2">
-        <v>9</v>
-      </c>
-      <c r="C322" s="2">
-        <v>9</v>
-      </c>
-      <c r="D322" s="2">
-        <v>0</v>
-      </c>
-      <c r="E322" s="2">
-        <v>5</v>
-      </c>
-      <c r="F322" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G322" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H322" s="2">
-        <v>78</v>
-      </c>
-      <c r="I322" s="2">
-        <v>11</v>
-      </c>
-      <c r="J322" s="2">
-        <v>67</v>
-      </c>
-      <c r="K322" s="2">
-        <v>0.9642857142857143</v>
-      </c>
-      <c r="L322" s="2">
-        <v>6.1858957413174209E-2</v>
-      </c>
-      <c r="M322" s="2">
-        <v>0.9375</v>
-      </c>
-      <c r="N322" s="2">
-        <v>0.1082531754730548</v>
-      </c>
-      <c r="O322" s="2">
-        <v>1</v>
-      </c>
-      <c r="P322" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q322" s="2">
-        <v>0.9375</v>
-      </c>
-      <c r="R322" s="2">
-        <v>0.1082531754730548</v>
-      </c>
-      <c r="S322" s="2">
-        <v>0.99038461538461542</v>
-      </c>
-      <c r="T322" s="2">
-        <v>1.665433468816227E-2</v>
-      </c>
-    </row>
-    <row r="323" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A323" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B323" s="2">
-        <v>9</v>
-      </c>
-      <c r="C323" s="2">
-        <v>9</v>
-      </c>
-      <c r="D323" s="2">
-        <v>0</v>
-      </c>
-      <c r="E323" s="2">
-        <v>5</v>
-      </c>
-      <c r="F323" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G323" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H323" s="2">
-        <v>78</v>
-      </c>
-      <c r="I323" s="2">
-        <v>11</v>
-      </c>
-      <c r="J323" s="2">
-        <v>67</v>
-      </c>
-      <c r="K323" s="2">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="L323" s="2">
-        <v>0.14433756729740641</v>
-      </c>
-      <c r="M323" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="N323" s="2">
-        <v>8.6602540378443879E-2</v>
-      </c>
-      <c r="O323" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="P323" s="2">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="Q323" s="2">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="R323" s="2">
-        <v>2.9315098498896439E-2</v>
-      </c>
-      <c r="S323" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T323" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="324" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A324" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B324" s="2">
-        <v>9</v>
-      </c>
-      <c r="C324" s="2">
-        <v>9</v>
-      </c>
-      <c r="D324" s="2">
-        <v>0</v>
-      </c>
-      <c r="E324" s="2">
-        <v>5</v>
-      </c>
-      <c r="F324" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G324" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H324" s="2">
-        <v>78</v>
-      </c>
-      <c r="I324" s="2">
-        <v>11</v>
-      </c>
-      <c r="J324" s="2">
-        <v>67</v>
-      </c>
-      <c r="K324" s="2">
-        <v>0.28749999999999998</v>
-      </c>
-      <c r="L324" s="2">
-        <v>0.18833148966649199</v>
-      </c>
-      <c r="M324" s="2">
-        <v>0.21309523809523809</v>
-      </c>
-      <c r="N324" s="2">
-        <v>0.14813179000769669</v>
-      </c>
-      <c r="O324" s="2">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="P324" s="2">
-        <v>0.27322660517925001</v>
-      </c>
-      <c r="Q324" s="2">
-        <v>0.31200396825396831</v>
-      </c>
-      <c r="R324" s="2">
-        <v>7.5616911966063835E-2</v>
-      </c>
-      <c r="S324" s="2">
-        <v>0.7123397435897435</v>
-      </c>
-      <c r="T324" s="2">
-        <v>7.0380667244831843E-2</v>
-      </c>
-    </row>
-    <row r="325" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A325" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B325" s="2">
-        <v>9</v>
-      </c>
-      <c r="C325" s="2">
-        <v>9</v>
-      </c>
-      <c r="D325" s="2">
-        <v>0</v>
-      </c>
-      <c r="E325" s="2">
-        <v>5</v>
-      </c>
-      <c r="F325" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G325" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H325" s="2">
-        <v>78</v>
-      </c>
-      <c r="I325" s="2">
-        <v>11</v>
-      </c>
-      <c r="J325" s="2">
-        <v>67</v>
-      </c>
-      <c r="K325" s="2">
-        <v>0.29678362573099409</v>
-      </c>
-      <c r="L325" s="2">
-        <v>4.3639799873097372E-2</v>
-      </c>
-      <c r="M325" s="2">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="N325" s="2">
-        <v>2.9315098498896439E-2</v>
-      </c>
-      <c r="O325" s="2">
-        <v>1</v>
-      </c>
-      <c r="P325" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q325" s="2">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="R325" s="2">
-        <v>2.9315098498896439E-2</v>
-      </c>
-      <c r="S325" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T325" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="326" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A326" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B326" s="2">
-        <v>10</v>
-      </c>
-      <c r="C326" s="2">
-        <v>10</v>
-      </c>
-      <c r="D326" s="2">
-        <v>0</v>
-      </c>
-      <c r="E326" s="2">
-        <v>5</v>
-      </c>
-      <c r="F326" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G326" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H326" s="2">
-        <v>33</v>
-      </c>
-      <c r="I326" s="2">
-        <v>8</v>
-      </c>
-      <c r="J326" s="2">
-        <v>25</v>
-      </c>
-      <c r="K326" s="2">
-        <v>0.875</v>
-      </c>
-      <c r="L326" s="2">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="M326" s="2">
-        <v>1</v>
-      </c>
-      <c r="N326" s="2">
-        <v>0</v>
-      </c>
-      <c r="O326" s="2">
-        <v>0.83333333333333326</v>
-      </c>
-      <c r="P326" s="2">
-        <v>0.28867513459481292</v>
-      </c>
-      <c r="Q326" s="2">
-        <v>1</v>
-      </c>
-      <c r="R326" s="2">
-        <v>0</v>
-      </c>
-      <c r="S326" s="2">
-        <v>1</v>
-      </c>
-      <c r="T326" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A327" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B327" s="2">
-        <v>10</v>
-      </c>
-      <c r="C327" s="2">
-        <v>10</v>
-      </c>
-      <c r="D327" s="2">
-        <v>0</v>
-      </c>
-      <c r="E327" s="2">
-        <v>5</v>
-      </c>
-      <c r="F327" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G327" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H327" s="2">
-        <v>33</v>
-      </c>
-      <c r="I327" s="2">
-        <v>8</v>
-      </c>
-      <c r="J327" s="2">
-        <v>25</v>
-      </c>
-      <c r="K327" s="2">
-        <v>0.22500000000000001</v>
-      </c>
-      <c r="L327" s="2">
-        <v>0.22776083947860751</v>
-      </c>
-      <c r="M327" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="N327" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="O327" s="2">
-        <v>0.20833333333333329</v>
-      </c>
-      <c r="P327" s="2">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="Q327" s="2">
-        <v>0.53363095238095237</v>
-      </c>
-      <c r="R327" s="2">
-        <v>0.21528927534946751</v>
-      </c>
-      <c r="S327" s="2">
-        <v>0.57916666666666661</v>
-      </c>
-      <c r="T327" s="2">
-        <v>0.2372806004150641</v>
-      </c>
-    </row>
-    <row r="328" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A328" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B328" s="2">
-        <v>10</v>
-      </c>
-      <c r="C328" s="2">
-        <v>10</v>
-      </c>
-      <c r="D328" s="2">
-        <v>0</v>
-      </c>
-      <c r="E328" s="2">
-        <v>5</v>
-      </c>
-      <c r="F328" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G328" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H328" s="2">
-        <v>33</v>
-      </c>
-      <c r="I328" s="2">
-        <v>8</v>
-      </c>
-      <c r="J328" s="2">
-        <v>25</v>
-      </c>
-      <c r="K328" s="2">
-        <v>0.875</v>
-      </c>
-      <c r="L328" s="2">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="M328" s="2">
-        <v>1</v>
-      </c>
-      <c r="N328" s="2">
-        <v>0</v>
-      </c>
-      <c r="O328" s="2">
-        <v>0.83333333333333326</v>
-      </c>
-      <c r="P328" s="2">
-        <v>0.28867513459481292</v>
-      </c>
-      <c r="Q328" s="2">
-        <v>1</v>
-      </c>
-      <c r="R328" s="2">
-        <v>0</v>
-      </c>
-      <c r="S328" s="2">
-        <v>1</v>
-      </c>
-      <c r="T328" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A329" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B329" s="2">
-        <v>10</v>
-      </c>
-      <c r="C329" s="2">
-        <v>10</v>
-      </c>
-      <c r="D329" s="2">
-        <v>0</v>
-      </c>
-      <c r="E329" s="2">
-        <v>5</v>
-      </c>
-      <c r="F329" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G329" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H329" s="2">
-        <v>33</v>
-      </c>
-      <c r="I329" s="2">
-        <v>8</v>
-      </c>
-      <c r="J329" s="2">
-        <v>25</v>
-      </c>
-      <c r="K329" s="2">
-        <v>0.875</v>
-      </c>
-      <c r="L329" s="2">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="M329" s="2">
-        <v>1</v>
-      </c>
-      <c r="N329" s="2">
-        <v>0</v>
-      </c>
-      <c r="O329" s="2">
-        <v>0.83333333333333326</v>
-      </c>
-      <c r="P329" s="2">
-        <v>0.28867513459481292</v>
-      </c>
-      <c r="Q329" s="2">
-        <v>1</v>
-      </c>
-      <c r="R329" s="2">
-        <v>0</v>
-      </c>
-      <c r="S329" s="2">
-        <v>1</v>
-      </c>
-      <c r="T329" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="330" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A330" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B330" s="2">
-        <v>10</v>
-      </c>
-      <c r="C330" s="2">
-        <v>10</v>
-      </c>
-      <c r="D330" s="2">
-        <v>0</v>
-      </c>
-      <c r="E330" s="2">
-        <v>5</v>
-      </c>
-      <c r="F330" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G330" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H330" s="2">
-        <v>33</v>
-      </c>
-      <c r="I330" s="2">
-        <v>8</v>
-      </c>
-      <c r="J330" s="2">
-        <v>25</v>
-      </c>
-      <c r="K330" s="2">
-        <v>0.875</v>
-      </c>
-      <c r="L330" s="2">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="M330" s="2">
-        <v>1</v>
-      </c>
-      <c r="N330" s="2">
-        <v>0</v>
-      </c>
-      <c r="O330" s="2">
-        <v>0.83333333333333326</v>
-      </c>
-      <c r="P330" s="2">
-        <v>0.28867513459481292</v>
-      </c>
-      <c r="Q330" s="2">
-        <v>1</v>
-      </c>
-      <c r="R330" s="2">
-        <v>0</v>
-      </c>
-      <c r="S330" s="2">
-        <v>1</v>
-      </c>
-      <c r="T330" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A331" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B331" s="2">
-        <v>10</v>
-      </c>
-      <c r="C331" s="2">
-        <v>10</v>
-      </c>
-      <c r="D331" s="2">
-        <v>0</v>
-      </c>
-      <c r="E331" s="2">
-        <v>5</v>
-      </c>
-      <c r="F331" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G331" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H331" s="2">
-        <v>33</v>
-      </c>
-      <c r="I331" s="2">
-        <v>8</v>
-      </c>
-      <c r="J331" s="2">
-        <v>25</v>
-      </c>
-      <c r="K331" s="2">
-        <v>0</v>
-      </c>
-      <c r="L331" s="2">
-        <v>0</v>
-      </c>
-      <c r="M331" s="2">
-        <v>0</v>
-      </c>
-      <c r="N331" s="2">
-        <v>0</v>
-      </c>
-      <c r="O331" s="2">
-        <v>0</v>
-      </c>
-      <c r="P331" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q331" s="2">
-        <v>0.29761904761904762</v>
-      </c>
-      <c r="R331" s="2">
-        <v>0.10309826235529029</v>
-      </c>
-      <c r="S331" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T331" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A332" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B332" s="2">
-        <v>10</v>
-      </c>
-      <c r="C332" s="2">
-        <v>10</v>
-      </c>
-      <c r="D332" s="2">
-        <v>0</v>
-      </c>
-      <c r="E332" s="2">
-        <v>5</v>
-      </c>
-      <c r="F332" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G332" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H332" s="2">
-        <v>33</v>
-      </c>
-      <c r="I332" s="2">
-        <v>8</v>
-      </c>
-      <c r="J332" s="2">
-        <v>25</v>
-      </c>
-      <c r="K332" s="2">
-        <v>0.26666666666666672</v>
-      </c>
-      <c r="L332" s="2">
-        <v>0.28284271247461901</v>
-      </c>
-      <c r="M332" s="2">
-        <v>0.375</v>
-      </c>
-      <c r="N332" s="2">
-        <v>0.41457809879442498</v>
-      </c>
-      <c r="O332" s="2">
-        <v>0.20833333333333329</v>
-      </c>
-      <c r="P332" s="2">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="Q332" s="2">
-        <v>0.57291666666666663</v>
-      </c>
-      <c r="R332" s="2">
-        <v>0.27609472760469572</v>
-      </c>
-      <c r="S332" s="2">
-        <v>0.61458333333333326</v>
-      </c>
-      <c r="T332" s="2">
-        <v>0.26902440771135328</v>
-      </c>
-    </row>
-    <row r="333" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A333" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B333" s="2">
-        <v>10</v>
-      </c>
-      <c r="C333" s="2">
-        <v>10</v>
-      </c>
-      <c r="D333" s="2">
-        <v>0</v>
-      </c>
-      <c r="E333" s="2">
-        <v>5</v>
-      </c>
-      <c r="F333" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G333" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H333" s="2">
-        <v>33</v>
-      </c>
-      <c r="I333" s="2">
-        <v>8</v>
-      </c>
-      <c r="J333" s="2">
-        <v>25</v>
-      </c>
-      <c r="K333" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="L333" s="2">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="M333" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="N333" s="2">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="O333" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="P333" s="2">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="Q333" s="2">
-        <v>1</v>
-      </c>
-      <c r="R333" s="2">
-        <v>0</v>
-      </c>
-      <c r="S333" s="2">
-        <v>1</v>
-      </c>
-      <c r="T333" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="334" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A334" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B334" s="2">
-        <v>10</v>
-      </c>
-      <c r="C334" s="2">
-        <v>10</v>
-      </c>
-      <c r="D334" s="2">
-        <v>0</v>
-      </c>
-      <c r="E334" s="2">
-        <v>5</v>
-      </c>
-      <c r="F334" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G334" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H334" s="2">
-        <v>33</v>
-      </c>
-      <c r="I334" s="2">
-        <v>8</v>
-      </c>
-      <c r="J334" s="2">
-        <v>25</v>
-      </c>
-      <c r="K334" s="2">
-        <v>0</v>
-      </c>
-      <c r="L334" s="2">
-        <v>0</v>
-      </c>
-      <c r="M334" s="2">
-        <v>0</v>
-      </c>
-      <c r="N334" s="2">
-        <v>0</v>
-      </c>
-      <c r="O334" s="2">
-        <v>0</v>
-      </c>
-      <c r="P334" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q334" s="2">
-        <v>0.70138888888888884</v>
-      </c>
-      <c r="R334" s="2">
-        <v>0.17388866702151271</v>
-      </c>
-      <c r="S334" s="2">
-        <v>0.83750000000000002</v>
-      </c>
-      <c r="T334" s="2">
-        <v>0.1023169096484056</v>
-      </c>
-    </row>
-    <row r="335" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A335" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B335" s="2">
-        <v>10</v>
-      </c>
-      <c r="C335" s="2">
-        <v>10</v>
-      </c>
-      <c r="D335" s="2">
-        <v>0</v>
-      </c>
-      <c r="E335" s="2">
-        <v>5</v>
-      </c>
-      <c r="F335" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G335" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H335" s="2">
-        <v>33</v>
-      </c>
-      <c r="I335" s="2">
-        <v>8</v>
-      </c>
-      <c r="J335" s="2">
-        <v>25</v>
-      </c>
-      <c r="K335" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="L335" s="2">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="M335" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="N335" s="2">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="O335" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="P335" s="2">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="Q335" s="2">
-        <v>1</v>
-      </c>
-      <c r="R335" s="2">
-        <v>0</v>
-      </c>
-      <c r="S335" s="2">
-        <v>1</v>
-      </c>
-      <c r="T335" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="336" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A336" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B336" s="2">
-        <v>10</v>
-      </c>
-      <c r="C336" s="2">
-        <v>10</v>
-      </c>
-      <c r="D336" s="2">
-        <v>0</v>
-      </c>
-      <c r="E336" s="2">
-        <v>5</v>
-      </c>
-      <c r="F336" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G336" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H336" s="2">
-        <v>33</v>
-      </c>
-      <c r="I336" s="2">
-        <v>8</v>
-      </c>
-      <c r="J336" s="2">
-        <v>25</v>
-      </c>
-      <c r="K336" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="L336" s="2">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="M336" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="N336" s="2">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="O336" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="P336" s="2">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="Q336" s="2">
-        <v>1</v>
-      </c>
-      <c r="R336" s="2">
-        <v>0</v>
-      </c>
-      <c r="S336" s="2">
-        <v>1</v>
-      </c>
-      <c r="T336" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A337" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B337" s="2">
-        <v>10</v>
-      </c>
-      <c r="C337" s="2">
-        <v>10</v>
-      </c>
-      <c r="D337" s="2">
-        <v>0</v>
-      </c>
-      <c r="E337" s="2">
-        <v>5</v>
-      </c>
-      <c r="F337" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G337" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H337" s="2">
-        <v>33</v>
-      </c>
-      <c r="I337" s="2">
-        <v>8</v>
-      </c>
-      <c r="J337" s="2">
-        <v>25</v>
-      </c>
-      <c r="K337" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="L337" s="2">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="M337" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="N337" s="2">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="O337" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="P337" s="2">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="Q337" s="2">
-        <v>1</v>
-      </c>
-      <c r="R337" s="2">
-        <v>0</v>
-      </c>
-      <c r="S337" s="2">
-        <v>1</v>
-      </c>
-      <c r="T337" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="338" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A338" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B338" s="2">
-        <v>10</v>
-      </c>
-      <c r="C338" s="2">
-        <v>10</v>
-      </c>
-      <c r="D338" s="2">
-        <v>0</v>
-      </c>
-      <c r="E338" s="2">
-        <v>5</v>
-      </c>
-      <c r="F338" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G338" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H338" s="2">
-        <v>33</v>
-      </c>
-      <c r="I338" s="2">
-        <v>8</v>
-      </c>
-      <c r="J338" s="2">
-        <v>25</v>
-      </c>
-      <c r="K338" s="2">
-        <v>0</v>
-      </c>
-      <c r="L338" s="2">
-        <v>0</v>
-      </c>
-      <c r="M338" s="2">
-        <v>0</v>
-      </c>
-      <c r="N338" s="2">
-        <v>0</v>
-      </c>
-      <c r="O338" s="2">
-        <v>0</v>
-      </c>
-      <c r="P338" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q338" s="2">
-        <v>0.29761904761904762</v>
-      </c>
-      <c r="R338" s="2">
-        <v>0.10309826235529029</v>
-      </c>
-      <c r="S338" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T338" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="339" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A339" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B339" s="2">
-        <v>10</v>
-      </c>
-      <c r="C339" s="2">
-        <v>10</v>
-      </c>
-      <c r="D339" s="2">
-        <v>0</v>
-      </c>
-      <c r="E339" s="2">
-        <v>5</v>
-      </c>
-      <c r="F339" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G339" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H339" s="2">
-        <v>33</v>
-      </c>
-      <c r="I339" s="2">
-        <v>8</v>
-      </c>
-      <c r="J339" s="2">
-        <v>25</v>
-      </c>
-      <c r="K339" s="2">
-        <v>0</v>
-      </c>
-      <c r="L339" s="2">
-        <v>0</v>
-      </c>
-      <c r="M339" s="2">
-        <v>0</v>
-      </c>
-      <c r="N339" s="2">
-        <v>0</v>
-      </c>
-      <c r="O339" s="2">
-        <v>0</v>
-      </c>
-      <c r="P339" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q339" s="2">
-        <v>0.78472222222222221</v>
-      </c>
-      <c r="R339" s="2">
-        <v>0.1804219591217581</v>
-      </c>
-      <c r="S339" s="2">
-        <v>0.83958333333333335</v>
-      </c>
-      <c r="T339" s="2">
-        <v>0.13735788109897451</v>
-      </c>
-    </row>
-    <row r="340" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A340" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B340" s="2">
-        <v>10</v>
-      </c>
-      <c r="C340" s="2">
-        <v>10</v>
-      </c>
-      <c r="D340" s="2">
-        <v>0</v>
-      </c>
-      <c r="E340" s="2">
-        <v>5</v>
-      </c>
-      <c r="F340" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G340" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H340" s="2">
-        <v>33</v>
-      </c>
-      <c r="I340" s="2">
-        <v>8</v>
-      </c>
-      <c r="J340" s="2">
-        <v>25</v>
-      </c>
-      <c r="K340" s="2">
-        <v>1</v>
-      </c>
-      <c r="L340" s="2">
-        <v>0</v>
-      </c>
-      <c r="M340" s="2">
-        <v>1</v>
-      </c>
-      <c r="N340" s="2">
-        <v>0</v>
-      </c>
-      <c r="O340" s="2">
-        <v>1</v>
-      </c>
-      <c r="P340" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q340" s="2">
-        <v>1</v>
-      </c>
-      <c r="R340" s="2">
-        <v>0</v>
-      </c>
-      <c r="S340" s="2">
-        <v>1</v>
-      </c>
-      <c r="T340" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="341" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A341" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B341" s="2">
-        <v>10</v>
-      </c>
-      <c r="C341" s="2">
-        <v>10</v>
-      </c>
-      <c r="D341" s="2">
-        <v>0</v>
-      </c>
-      <c r="E341" s="2">
-        <v>5</v>
-      </c>
-      <c r="F341" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G341" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H341" s="2">
-        <v>33</v>
-      </c>
-      <c r="I341" s="2">
-        <v>8</v>
-      </c>
-      <c r="J341" s="2">
-        <v>25</v>
-      </c>
-      <c r="K341" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="L341" s="2">
-        <v>0.17320508075688781</v>
-      </c>
-      <c r="M341" s="2">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="N341" s="2">
-        <v>0.14433756729740641</v>
-      </c>
-      <c r="O341" s="2">
-        <v>0.125</v>
-      </c>
-      <c r="P341" s="2">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="Q341" s="2">
-        <v>0.46418650793650801</v>
-      </c>
-      <c r="R341" s="2">
-        <v>0.19461653685934091</v>
-      </c>
-      <c r="S341" s="2">
-        <v>0.53749999999999998</v>
-      </c>
-      <c r="T341" s="2">
-        <v>0.12930100540985751</v>
-      </c>
-    </row>
-    <row r="342" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A342" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B342" s="2">
-        <v>10</v>
-      </c>
-      <c r="C342" s="2">
-        <v>10</v>
-      </c>
-      <c r="D342" s="2">
-        <v>0</v>
-      </c>
-      <c r="E342" s="2">
-        <v>5</v>
-      </c>
-      <c r="F342" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G342" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H342" s="2">
-        <v>33</v>
-      </c>
-      <c r="I342" s="2">
-        <v>8</v>
-      </c>
-      <c r="J342" s="2">
-        <v>25</v>
-      </c>
-      <c r="K342" s="2">
-        <v>1</v>
-      </c>
-      <c r="L342" s="2">
-        <v>0</v>
-      </c>
-      <c r="M342" s="2">
-        <v>1</v>
-      </c>
-      <c r="N342" s="2">
-        <v>0</v>
-      </c>
-      <c r="O342" s="2">
-        <v>1</v>
-      </c>
-      <c r="P342" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q342" s="2">
-        <v>1</v>
-      </c>
-      <c r="R342" s="2">
-        <v>0</v>
-      </c>
-      <c r="S342" s="2">
-        <v>1</v>
-      </c>
-      <c r="T342" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="343" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A343" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B343" s="2">
-        <v>10</v>
-      </c>
-      <c r="C343" s="2">
-        <v>10</v>
-      </c>
-      <c r="D343" s="2">
-        <v>0</v>
-      </c>
-      <c r="E343" s="2">
-        <v>5</v>
-      </c>
-      <c r="F343" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G343" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H343" s="2">
-        <v>33</v>
-      </c>
-      <c r="I343" s="2">
-        <v>8</v>
-      </c>
-      <c r="J343" s="2">
-        <v>25</v>
-      </c>
-      <c r="K343" s="2">
-        <v>1</v>
-      </c>
-      <c r="L343" s="2">
-        <v>0</v>
-      </c>
-      <c r="M343" s="2">
-        <v>1</v>
-      </c>
-      <c r="N343" s="2">
-        <v>0</v>
-      </c>
-      <c r="O343" s="2">
-        <v>1</v>
-      </c>
-      <c r="P343" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q343" s="2">
-        <v>1</v>
-      </c>
-      <c r="R343" s="2">
-        <v>0</v>
-      </c>
-      <c r="S343" s="2">
-        <v>1</v>
-      </c>
-      <c r="T343" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="344" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A344" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B344" s="2">
-        <v>10</v>
-      </c>
-      <c r="C344" s="2">
-        <v>10</v>
-      </c>
-      <c r="D344" s="2">
-        <v>0</v>
-      </c>
-      <c r="E344" s="2">
-        <v>5</v>
-      </c>
-      <c r="F344" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G344" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H344" s="2">
-        <v>33</v>
-      </c>
-      <c r="I344" s="2">
-        <v>8</v>
-      </c>
-      <c r="J344" s="2">
-        <v>25</v>
-      </c>
-      <c r="K344" s="2">
-        <v>1</v>
-      </c>
-      <c r="L344" s="2">
-        <v>0</v>
-      </c>
-      <c r="M344" s="2">
-        <v>1</v>
-      </c>
-      <c r="N344" s="2">
-        <v>0</v>
-      </c>
-      <c r="O344" s="2">
-        <v>1</v>
-      </c>
-      <c r="P344" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q344" s="2">
-        <v>1</v>
-      </c>
-      <c r="R344" s="2">
-        <v>0</v>
-      </c>
-      <c r="S344" s="2">
-        <v>1</v>
-      </c>
-      <c r="T344" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="345" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A345" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B345" s="2">
-        <v>10</v>
-      </c>
-      <c r="C345" s="2">
-        <v>10</v>
-      </c>
-      <c r="D345" s="2">
-        <v>0</v>
-      </c>
-      <c r="E345" s="2">
-        <v>5</v>
-      </c>
-      <c r="F345" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G345" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H345" s="2">
-        <v>33</v>
-      </c>
-      <c r="I345" s="2">
-        <v>8</v>
-      </c>
-      <c r="J345" s="2">
-        <v>25</v>
-      </c>
-      <c r="K345" s="2">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="L345" s="2">
-        <v>0.19245008972987529</v>
-      </c>
-      <c r="M345" s="2">
-        <v>7.1428571428571425E-2</v>
-      </c>
-      <c r="N345" s="2">
-        <v>0.1237179148263484</v>
-      </c>
-      <c r="O345" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="P345" s="2">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="Q345" s="2">
-        <v>0.29761904761904762</v>
-      </c>
-      <c r="R345" s="2">
-        <v>0.10309826235529029</v>
-      </c>
-      <c r="S345" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T345" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A346" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B346" s="2">
-        <v>10</v>
-      </c>
-      <c r="C346" s="2">
-        <v>10</v>
-      </c>
-      <c r="D346" s="2">
-        <v>0</v>
-      </c>
-      <c r="E346" s="2">
-        <v>5</v>
-      </c>
-      <c r="F346" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G346" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H346" s="2">
-        <v>33</v>
-      </c>
-      <c r="I346" s="2">
-        <v>8</v>
-      </c>
-      <c r="J346" s="2">
-        <v>25</v>
-      </c>
-      <c r="K346" s="2">
-        <v>0.16666666666666671</v>
-      </c>
-      <c r="L346" s="2">
-        <v>0.28867513459481292</v>
-      </c>
-      <c r="M346" s="2">
-        <v>0.125</v>
-      </c>
-      <c r="N346" s="2">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="O346" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="P346" s="2">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="Q346" s="2">
-        <v>0.46418650793650801</v>
-      </c>
-      <c r="R346" s="2">
-        <v>0.19461653685934091</v>
-      </c>
-      <c r="S346" s="2">
-        <v>0.53749999999999998</v>
-      </c>
-      <c r="T346" s="2">
-        <v>0.12930100540985751</v>
-      </c>
-    </row>
-    <row r="347" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A347" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B347" s="2">
-        <v>10</v>
-      </c>
-      <c r="C347" s="2">
-        <v>10</v>
-      </c>
-      <c r="D347" s="2">
-        <v>0</v>
-      </c>
-      <c r="E347" s="2">
-        <v>5</v>
-      </c>
-      <c r="F347" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G347" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H347" s="2">
-        <v>33</v>
-      </c>
-      <c r="I347" s="2">
-        <v>8</v>
-      </c>
-      <c r="J347" s="2">
-        <v>25</v>
-      </c>
-      <c r="K347" s="2">
-        <v>1</v>
-      </c>
-      <c r="L347" s="2">
-        <v>0</v>
-      </c>
-      <c r="M347" s="2">
-        <v>1</v>
-      </c>
-      <c r="N347" s="2">
-        <v>0</v>
-      </c>
-      <c r="O347" s="2">
-        <v>1</v>
-      </c>
-      <c r="P347" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q347" s="2">
-        <v>1</v>
-      </c>
-      <c r="R347" s="2">
-        <v>0</v>
-      </c>
-      <c r="S347" s="2">
-        <v>1</v>
-      </c>
-      <c r="T347" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="348" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A348" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B348" s="2">
-        <v>10</v>
-      </c>
-      <c r="C348" s="2">
-        <v>10</v>
-      </c>
-      <c r="D348" s="2">
-        <v>0</v>
-      </c>
-      <c r="E348" s="2">
-        <v>5</v>
-      </c>
-      <c r="F348" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G348" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H348" s="2">
-        <v>33</v>
-      </c>
-      <c r="I348" s="2">
-        <v>8</v>
-      </c>
-      <c r="J348" s="2">
-        <v>25</v>
-      </c>
-      <c r="K348" s="2">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="L348" s="2">
-        <v>0.14433756729740641</v>
-      </c>
-      <c r="M348" s="2">
-        <v>6.25E-2</v>
-      </c>
-      <c r="N348" s="2">
-        <v>0.1082531754730548</v>
-      </c>
-      <c r="O348" s="2">
-        <v>0.125</v>
-      </c>
-      <c r="P348" s="2">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="Q348" s="2">
-        <v>0.42946428571428569</v>
-      </c>
-      <c r="R348" s="2">
-        <v>0.1778823510375821</v>
-      </c>
-      <c r="S348" s="2">
-        <v>0.46041666666666659</v>
-      </c>
-      <c r="T348" s="2">
-        <v>0.11864030020753211</v>
-      </c>
-    </row>
-    <row r="349" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A349" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B349" s="2">
-        <v>10</v>
-      </c>
-      <c r="C349" s="2">
-        <v>10</v>
-      </c>
-      <c r="D349" s="2">
-        <v>0</v>
-      </c>
-      <c r="E349" s="2">
-        <v>5</v>
-      </c>
-      <c r="F349" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G349" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H349" s="2">
-        <v>33</v>
-      </c>
-      <c r="I349" s="2">
-        <v>8</v>
-      </c>
-      <c r="J349" s="2">
-        <v>25</v>
-      </c>
-      <c r="K349" s="2">
-        <v>1</v>
-      </c>
-      <c r="L349" s="2">
-        <v>0</v>
-      </c>
-      <c r="M349" s="2">
-        <v>1</v>
-      </c>
-      <c r="N349" s="2">
-        <v>0</v>
-      </c>
-      <c r="O349" s="2">
-        <v>1</v>
-      </c>
-      <c r="P349" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q349" s="2">
-        <v>1</v>
-      </c>
-      <c r="R349" s="2">
-        <v>0</v>
-      </c>
-      <c r="S349" s="2">
-        <v>1</v>
-      </c>
-      <c r="T349" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A350" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B350" s="2">
-        <v>10</v>
-      </c>
-      <c r="C350" s="2">
-        <v>10</v>
-      </c>
-      <c r="D350" s="2">
-        <v>0</v>
-      </c>
-      <c r="E350" s="2">
-        <v>5</v>
-      </c>
-      <c r="F350" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G350" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H350" s="2">
-        <v>33</v>
-      </c>
-      <c r="I350" s="2">
-        <v>8</v>
-      </c>
-      <c r="J350" s="2">
-        <v>25</v>
-      </c>
-      <c r="K350" s="2">
-        <v>1</v>
-      </c>
-      <c r="L350" s="2">
-        <v>0</v>
-      </c>
-      <c r="M350" s="2">
-        <v>1</v>
-      </c>
-      <c r="N350" s="2">
-        <v>0</v>
-      </c>
-      <c r="O350" s="2">
-        <v>1</v>
-      </c>
-      <c r="P350" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q350" s="2">
-        <v>1</v>
-      </c>
-      <c r="R350" s="2">
-        <v>0</v>
-      </c>
-      <c r="S350" s="2">
-        <v>1</v>
-      </c>
-      <c r="T350" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="351" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A351" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B351" s="2">
-        <v>10</v>
-      </c>
-      <c r="C351" s="2">
-        <v>10</v>
-      </c>
-      <c r="D351" s="2">
-        <v>0</v>
-      </c>
-      <c r="E351" s="2">
-        <v>5</v>
-      </c>
-      <c r="F351" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G351" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H351" s="2">
-        <v>33</v>
-      </c>
-      <c r="I351" s="2">
-        <v>8</v>
-      </c>
-      <c r="J351" s="2">
-        <v>25</v>
-      </c>
-      <c r="K351" s="2">
-        <v>1</v>
-      </c>
-      <c r="L351" s="2">
-        <v>0</v>
-      </c>
-      <c r="M351" s="2">
-        <v>1</v>
-      </c>
-      <c r="N351" s="2">
-        <v>0</v>
-      </c>
-      <c r="O351" s="2">
-        <v>1</v>
-      </c>
-      <c r="P351" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q351" s="2">
-        <v>1</v>
-      </c>
-      <c r="R351" s="2">
-        <v>0</v>
-      </c>
-      <c r="S351" s="2">
-        <v>1</v>
-      </c>
-      <c r="T351" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="352" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A352" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B352" s="2">
-        <v>10</v>
-      </c>
-      <c r="C352" s="2">
-        <v>10</v>
-      </c>
-      <c r="D352" s="2">
-        <v>0</v>
-      </c>
-      <c r="E352" s="2">
-        <v>5</v>
-      </c>
-      <c r="F352" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G352" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H352" s="2">
-        <v>33</v>
-      </c>
-      <c r="I352" s="2">
-        <v>8</v>
-      </c>
-      <c r="J352" s="2">
-        <v>25</v>
-      </c>
-      <c r="K352" s="2">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="L352" s="2">
-        <v>0.19245008972987529</v>
-      </c>
-      <c r="M352" s="2">
-        <v>7.1428571428571425E-2</v>
-      </c>
-      <c r="N352" s="2">
-        <v>0.1237179148263484</v>
-      </c>
-      <c r="O352" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="P352" s="2">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="Q352" s="2">
-        <v>0.29761904761904762</v>
-      </c>
-      <c r="R352" s="2">
-        <v>0.10309826235529029</v>
-      </c>
-      <c r="S352" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T352" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="353" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A353" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B353" s="2">
-        <v>10</v>
-      </c>
-      <c r="C353" s="2">
-        <v>10</v>
-      </c>
-      <c r="D353" s="2">
-        <v>0</v>
-      </c>
-      <c r="E353" s="2">
-        <v>5</v>
-      </c>
-      <c r="F353" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G353" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H353" s="2">
-        <v>33</v>
-      </c>
-      <c r="I353" s="2">
-        <v>8</v>
-      </c>
-      <c r="J353" s="2">
-        <v>25</v>
-      </c>
-      <c r="K353" s="2">
-        <v>0.16666666666666671</v>
-      </c>
-      <c r="L353" s="2">
-        <v>0.28867513459481292</v>
-      </c>
-      <c r="M353" s="2">
-        <v>0.125</v>
-      </c>
-      <c r="N353" s="2">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="O353" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="P353" s="2">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="Q353" s="2">
-        <v>0.36001984126984121</v>
-      </c>
-      <c r="R353" s="2">
-        <v>0.12547634578015149</v>
-      </c>
-      <c r="S353" s="2">
-        <v>0.40833333333333333</v>
-      </c>
-      <c r="T353" s="2">
-        <v>9.2421137553411803E-2</v>
-      </c>
-    </row>
-    <row r="354" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A354" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B354" s="2">
-        <v>10</v>
-      </c>
-      <c r="C354" s="2">
-        <v>10</v>
-      </c>
-      <c r="D354" s="2">
-        <v>0</v>
-      </c>
-      <c r="E354" s="2">
-        <v>5</v>
-      </c>
-      <c r="F354" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G354" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H354" s="2">
-        <v>33</v>
-      </c>
-      <c r="I354" s="2">
-        <v>8</v>
-      </c>
-      <c r="J354" s="2">
-        <v>25</v>
-      </c>
-      <c r="K354" s="2">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L354" s="2">
-        <v>0.14877975892797601</v>
-      </c>
-      <c r="M354" s="2">
-        <v>0.77500000000000002</v>
-      </c>
-      <c r="N354" s="2">
-        <v>0.22776083947860751</v>
-      </c>
-      <c r="O354" s="2">
-        <v>1</v>
-      </c>
-      <c r="P354" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q354" s="2">
-        <v>0.77500000000000002</v>
-      </c>
-      <c r="R354" s="2">
-        <v>0.22776083947860751</v>
-      </c>
-      <c r="S354" s="2">
-        <v>0.88749999999999996</v>
-      </c>
-      <c r="T354" s="2">
-        <v>0.1138804197393037</v>
-      </c>
-    </row>
-    <row r="355" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A355" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B355" s="2">
-        <v>10</v>
-      </c>
-      <c r="C355" s="2">
-        <v>10</v>
-      </c>
-      <c r="D355" s="2">
-        <v>0</v>
-      </c>
-      <c r="E355" s="2">
-        <v>5</v>
-      </c>
-      <c r="F355" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G355" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H355" s="2">
-        <v>33</v>
-      </c>
-      <c r="I355" s="2">
-        <v>8</v>
-      </c>
-      <c r="J355" s="2">
-        <v>25</v>
-      </c>
-      <c r="K355" s="2">
-        <v>0.63452380952380949</v>
-      </c>
-      <c r="L355" s="2">
-        <v>0.11235345708845761</v>
-      </c>
-      <c r="M355" s="2">
-        <v>0.51666666666666661</v>
-      </c>
-      <c r="N355" s="2">
-        <v>0.15184055965240489</v>
-      </c>
-      <c r="O355" s="2">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="P355" s="2">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="Q355" s="2">
-        <v>0.49682539682539678</v>
-      </c>
-      <c r="R355" s="2">
-        <v>0.13521909099648929</v>
-      </c>
-      <c r="S355" s="2">
-        <v>0.76666666666666672</v>
-      </c>
-      <c r="T355" s="2">
-        <v>0.1068812944865055</v>
-      </c>
-    </row>
-    <row r="356" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A356" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B356" s="2">
-        <v>10</v>
-      </c>
-      <c r="C356" s="2">
-        <v>10</v>
-      </c>
-      <c r="D356" s="2">
-        <v>0</v>
-      </c>
-      <c r="E356" s="2">
-        <v>5</v>
-      </c>
-      <c r="F356" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G356" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H356" s="2">
-        <v>33</v>
-      </c>
-      <c r="I356" s="2">
-        <v>8</v>
-      </c>
-      <c r="J356" s="2">
-        <v>25</v>
-      </c>
-      <c r="K356" s="2">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L356" s="2">
-        <v>0.14877975892797601</v>
-      </c>
-      <c r="M356" s="2">
-        <v>0.77500000000000002</v>
-      </c>
-      <c r="N356" s="2">
-        <v>0.22776083947860751</v>
-      </c>
-      <c r="O356" s="2">
-        <v>1</v>
-      </c>
-      <c r="P356" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q356" s="2">
-        <v>0.77500000000000002</v>
-      </c>
-      <c r="R356" s="2">
-        <v>0.22776083947860751</v>
-      </c>
-      <c r="S356" s="2">
-        <v>0.88749999999999996</v>
-      </c>
-      <c r="T356" s="2">
-        <v>0.1138804197393037</v>
-      </c>
-    </row>
-    <row r="357" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A357" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B357" s="2">
-        <v>10</v>
-      </c>
-      <c r="C357" s="2">
-        <v>10</v>
-      </c>
-      <c r="D357" s="2">
-        <v>0</v>
-      </c>
-      <c r="E357" s="2">
-        <v>5</v>
-      </c>
-      <c r="F357" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G357" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H357" s="2">
-        <v>33</v>
-      </c>
-      <c r="I357" s="2">
-        <v>8</v>
-      </c>
-      <c r="J357" s="2">
-        <v>25</v>
-      </c>
-      <c r="K357" s="2">
-        <v>0.6791666666666667</v>
-      </c>
-      <c r="L357" s="2">
-        <v>0.1138804197393037</v>
-      </c>
-      <c r="M357" s="2">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="N357" s="2">
-        <v>0.12555432644432801</v>
-      </c>
-      <c r="O357" s="2">
-        <v>1</v>
-      </c>
-      <c r="P357" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q357" s="2">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="R357" s="2">
-        <v>0.12555432644432801</v>
-      </c>
-      <c r="S357" s="2">
-        <v>0.81458333333333333</v>
-      </c>
-      <c r="T357" s="2">
-        <v>4.5785960366324811E-2</v>
-      </c>
-    </row>
-    <row r="358" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A358" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B358" s="2">
-        <v>10</v>
-      </c>
-      <c r="C358" s="2">
-        <v>10</v>
-      </c>
-      <c r="D358" s="2">
-        <v>0</v>
-      </c>
-      <c r="E358" s="2">
-        <v>5</v>
-      </c>
-      <c r="F358" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G358" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H358" s="2">
-        <v>33</v>
-      </c>
-      <c r="I358" s="2">
-        <v>8</v>
-      </c>
-      <c r="J358" s="2">
-        <v>25</v>
-      </c>
-      <c r="K358" s="2">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L358" s="2">
-        <v>0.14877975892797601</v>
-      </c>
-      <c r="M358" s="2">
-        <v>0.77500000000000002</v>
-      </c>
-      <c r="N358" s="2">
-        <v>0.22776083947860751</v>
-      </c>
-      <c r="O358" s="2">
-        <v>1</v>
-      </c>
-      <c r="P358" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q358" s="2">
-        <v>0.77500000000000002</v>
-      </c>
-      <c r="R358" s="2">
-        <v>0.22776083947860751</v>
-      </c>
-      <c r="S358" s="2">
-        <v>0.88749999999999996</v>
-      </c>
-      <c r="T358" s="2">
-        <v>0.1138804197393037</v>
-      </c>
-    </row>
-    <row r="359" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A359" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B359" s="2">
-        <v>10</v>
-      </c>
-      <c r="C359" s="2">
-        <v>10</v>
-      </c>
-      <c r="D359" s="2">
-        <v>0</v>
-      </c>
-      <c r="E359" s="2">
-        <v>5</v>
-      </c>
-      <c r="F359" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G359" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H359" s="2">
-        <v>33</v>
-      </c>
-      <c r="I359" s="2">
-        <v>8</v>
-      </c>
-      <c r="J359" s="2">
-        <v>25</v>
-      </c>
-      <c r="K359" s="2">
-        <v>0.2361111111111111</v>
-      </c>
-      <c r="L359" s="2">
-        <v>0.2369266959615553</v>
-      </c>
-      <c r="M359" s="2">
-        <v>0.15476190476190479</v>
-      </c>
-      <c r="N359" s="2">
-        <v>0.1556749622693098</v>
-      </c>
-      <c r="O359" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="P359" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="Q359" s="2">
-        <v>0.29761904761904762</v>
-      </c>
-      <c r="R359" s="2">
-        <v>0.10309826235529029</v>
-      </c>
-      <c r="S359" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T359" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="360" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A360" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B360" s="2">
-        <v>10</v>
-      </c>
-      <c r="C360" s="2">
-        <v>10</v>
-      </c>
-      <c r="D360" s="2">
-        <v>0</v>
-      </c>
-      <c r="E360" s="2">
-        <v>5</v>
-      </c>
-      <c r="F360" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G360" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H360" s="2">
-        <v>33</v>
-      </c>
-      <c r="I360" s="2">
-        <v>8</v>
-      </c>
-      <c r="J360" s="2">
-        <v>25</v>
-      </c>
-      <c r="K360" s="2">
-        <v>0.63452380952380949</v>
-      </c>
-      <c r="L360" s="2">
-        <v>0.11235345708845761</v>
-      </c>
-      <c r="M360" s="2">
-        <v>0.51666666666666661</v>
-      </c>
-      <c r="N360" s="2">
-        <v>0.15184055965240489</v>
-      </c>
-      <c r="O360" s="2">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="P360" s="2">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="Q360" s="2">
-        <v>0.49682539682539678</v>
-      </c>
-      <c r="R360" s="2">
-        <v>0.13521909099648929</v>
-      </c>
-      <c r="S360" s="2">
-        <v>0.76666666666666672</v>
-      </c>
-      <c r="T360" s="2">
-        <v>0.1068812944865055</v>
-      </c>
-    </row>
-    <row r="361" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A361" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B361" s="2">
-        <v>10</v>
-      </c>
-      <c r="C361" s="2">
-        <v>10</v>
-      </c>
-      <c r="D361" s="2">
-        <v>0</v>
-      </c>
-      <c r="E361" s="2">
-        <v>5</v>
-      </c>
-      <c r="F361" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G361" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H361" s="2">
-        <v>33</v>
-      </c>
-      <c r="I361" s="2">
-        <v>8</v>
-      </c>
-      <c r="J361" s="2">
-        <v>25</v>
-      </c>
-      <c r="K361" s="2">
-        <v>0.44861111111111113</v>
-      </c>
-      <c r="L361" s="2">
-        <v>0.12749818444604241</v>
-      </c>
-      <c r="M361" s="2">
-        <v>0.29761904761904762</v>
-      </c>
-      <c r="N361" s="2">
-        <v>0.10309826235529029</v>
-      </c>
-      <c r="O361" s="2">
-        <v>1</v>
-      </c>
-      <c r="P361" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q361" s="2">
-        <v>0.29761904761904762</v>
-      </c>
-      <c r="R361" s="2">
-        <v>0.10309826235529029</v>
-      </c>
-      <c r="S361" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T361" s="2">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:T361" xr:uid="{00000000-0001-0000-0300-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T361">
-      <sortCondition ref="B1:B361"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:T289" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/RESULTS/climatenewsfr/climatenewsfr_results.xlsx
+++ b/RESULTS/climatenewsfr/climatenewsfr_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evangeliazve/Documents/Papier EMNLP/Dossier Github - supp material/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DEC9C47-5C1C-8A46-A7C4-594CB88AA948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974EB9F4-283C-684F-BC63-5726B02EE0F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31880" yWindow="8340" windowWidth="29400" windowHeight="17000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31880" yWindow="4600" windowWidth="29400" windowHeight="17000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ml_metrics_with_ablation" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="33">
   <si>
     <t>toa_max_neg</t>
   </si>
@@ -525,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:S361"/>
+  <dimension ref="A1:S289"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="7" width="19" customWidth="1"/>
@@ -17584,4262 +17584,8 @@
         <v>0.20018899499631759</v>
       </c>
     </row>
-    <row r="290" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A290" s="2">
-        <v>9</v>
-      </c>
-      <c r="B290" s="2">
-        <v>9</v>
-      </c>
-      <c r="C290" s="2">
-        <v>0</v>
-      </c>
-      <c r="D290" s="2">
-        <v>5</v>
-      </c>
-      <c r="E290" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F290" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G290" s="2">
-        <v>78</v>
-      </c>
-      <c r="H290" s="2">
-        <v>11</v>
-      </c>
-      <c r="I290" s="2">
-        <v>67</v>
-      </c>
-      <c r="J290" s="4">
-        <v>0.29678362573099409</v>
-      </c>
-      <c r="K290" s="4">
-        <v>4.3639799873097372E-2</v>
-      </c>
-      <c r="L290" s="4">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="M290" s="4">
-        <v>2.9315098498896439E-2</v>
-      </c>
-      <c r="N290" s="4">
-        <v>1</v>
-      </c>
-      <c r="O290" s="4">
-        <v>0</v>
-      </c>
-      <c r="P290" s="4">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="Q290" s="4">
-        <v>2.9315098498896439E-2</v>
-      </c>
-      <c r="R290" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="S290" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="291" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A291" s="2">
-        <v>9</v>
-      </c>
-      <c r="B291" s="2">
-        <v>9</v>
-      </c>
-      <c r="C291" s="2">
-        <v>0</v>
-      </c>
-      <c r="D291" s="2">
-        <v>5</v>
-      </c>
-      <c r="E291" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F291" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G291" s="2">
-        <v>78</v>
-      </c>
-      <c r="H291" s="2">
-        <v>11</v>
-      </c>
-      <c r="I291" s="2">
-        <v>67</v>
-      </c>
-      <c r="J291" s="4">
-        <v>0.87857142857142856</v>
-      </c>
-      <c r="K291" s="4">
-        <v>7.388628880563286E-2</v>
-      </c>
-      <c r="L291" s="4">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="M291" s="4">
-        <v>0.125</v>
-      </c>
-      <c r="N291" s="4">
-        <v>1</v>
-      </c>
-      <c r="O291" s="4">
-        <v>0</v>
-      </c>
-      <c r="P291" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q291" s="4">
-        <v>0</v>
-      </c>
-      <c r="R291" s="4">
-        <v>1</v>
-      </c>
-      <c r="S291" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="292" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A292" s="2">
-        <v>9</v>
-      </c>
-      <c r="B292" s="2">
-        <v>9</v>
-      </c>
-      <c r="C292" s="2">
-        <v>0</v>
-      </c>
-      <c r="D292" s="2">
-        <v>5</v>
-      </c>
-      <c r="E292" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F292" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G292" s="2">
-        <v>78</v>
-      </c>
-      <c r="H292" s="2">
-        <v>11</v>
-      </c>
-      <c r="I292" s="2">
-        <v>67</v>
-      </c>
-      <c r="J292" s="4">
-        <v>0.88095238095238093</v>
-      </c>
-      <c r="K292" s="4">
-        <v>0.13677530110804831</v>
-      </c>
-      <c r="L292" s="4">
-        <v>0.9375</v>
-      </c>
-      <c r="M292" s="4">
-        <v>0.1082531754730548</v>
-      </c>
-      <c r="N292" s="4">
-        <v>0.875</v>
-      </c>
-      <c r="O292" s="4">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="P292" s="4">
-        <v>0.890625</v>
-      </c>
-      <c r="Q292" s="4">
-        <v>0.18944305707784589</v>
-      </c>
-      <c r="R292" s="4">
-        <v>0.875</v>
-      </c>
-      <c r="S292" s="4">
-        <v>0.21650635094610959</v>
-      </c>
-    </row>
-    <row r="293" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A293" s="2">
-        <v>9</v>
-      </c>
-      <c r="B293" s="2">
-        <v>9</v>
-      </c>
-      <c r="C293" s="2">
-        <v>0</v>
-      </c>
-      <c r="D293" s="2">
-        <v>5</v>
-      </c>
-      <c r="E293" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F293" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G293" s="2">
-        <v>78</v>
-      </c>
-      <c r="H293" s="2">
-        <v>11</v>
-      </c>
-      <c r="I293" s="2">
-        <v>67</v>
-      </c>
-      <c r="J293" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="K293" s="4">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="L293" s="4">
-        <v>1</v>
-      </c>
-      <c r="M293" s="4">
-        <v>0</v>
-      </c>
-      <c r="N293" s="4">
-        <v>0.875</v>
-      </c>
-      <c r="O293" s="4">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="P293" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q293" s="4">
-        <v>0</v>
-      </c>
-      <c r="R293" s="4">
-        <v>1</v>
-      </c>
-      <c r="S293" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A294" s="2">
-        <v>9</v>
-      </c>
-      <c r="B294" s="2">
-        <v>9</v>
-      </c>
-      <c r="C294" s="2">
-        <v>0</v>
-      </c>
-      <c r="D294" s="2">
-        <v>5</v>
-      </c>
-      <c r="E294" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F294" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G294" s="2">
-        <v>78</v>
-      </c>
-      <c r="H294" s="2">
-        <v>11</v>
-      </c>
-      <c r="I294" s="2">
-        <v>67</v>
-      </c>
-      <c r="J294" s="4">
-        <v>0.9642857142857143</v>
-      </c>
-      <c r="K294" s="4">
-        <v>6.1858957413174209E-2</v>
-      </c>
-      <c r="L294" s="4">
-        <v>0.9375</v>
-      </c>
-      <c r="M294" s="4">
-        <v>0.1082531754730548</v>
-      </c>
-      <c r="N294" s="4">
-        <v>1</v>
-      </c>
-      <c r="O294" s="4">
-        <v>0</v>
-      </c>
-      <c r="P294" s="4">
-        <v>0.9375</v>
-      </c>
-      <c r="Q294" s="4">
-        <v>0.1082531754730548</v>
-      </c>
-      <c r="R294" s="4">
-        <v>0.99038461538461542</v>
-      </c>
-      <c r="S294" s="4">
-        <v>1.665433468816227E-2</v>
-      </c>
-    </row>
-    <row r="295" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A295" s="2">
-        <v>9</v>
-      </c>
-      <c r="B295" s="2">
-        <v>9</v>
-      </c>
-      <c r="C295" s="2">
-        <v>0</v>
-      </c>
-      <c r="D295" s="2">
-        <v>5</v>
-      </c>
-      <c r="E295" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F295" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G295" s="2">
-        <v>78</v>
-      </c>
-      <c r="H295" s="2">
-        <v>11</v>
-      </c>
-      <c r="I295" s="2">
-        <v>67</v>
-      </c>
-      <c r="J295" s="4">
-        <v>0.95</v>
-      </c>
-      <c r="K295" s="4">
-        <v>8.6602540378443851E-2</v>
-      </c>
-      <c r="L295" s="4">
-        <v>1</v>
-      </c>
-      <c r="M295" s="4">
-        <v>0</v>
-      </c>
-      <c r="N295" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="O295" s="4">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="P295" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q295" s="4">
-        <v>0</v>
-      </c>
-      <c r="R295" s="4">
-        <v>1</v>
-      </c>
-      <c r="S295" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="296" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A296" s="2">
-        <v>9</v>
-      </c>
-      <c r="B296" s="2">
-        <v>9</v>
-      </c>
-      <c r="C296" s="2">
-        <v>0</v>
-      </c>
-      <c r="D296" s="2">
-        <v>5</v>
-      </c>
-      <c r="E296" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F296" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G296" s="2">
-        <v>78</v>
-      </c>
-      <c r="H296" s="2">
-        <v>11</v>
-      </c>
-      <c r="I296" s="2">
-        <v>67</v>
-      </c>
-      <c r="J296" s="4">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="K296" s="4">
-        <v>0.1020620726159658</v>
-      </c>
-      <c r="L296" s="4">
-        <v>0.27500000000000002</v>
-      </c>
-      <c r="M296" s="4">
-        <v>9.5379359518829976E-2</v>
-      </c>
-      <c r="N296" s="4">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="O296" s="4">
-        <v>0.13819269959814159</v>
-      </c>
-      <c r="P296" s="4">
-        <v>0.51884920634920628</v>
-      </c>
-      <c r="Q296" s="4">
-        <v>0.12413485568553879</v>
-      </c>
-      <c r="R296" s="4">
-        <v>0.78548534798534808</v>
-      </c>
-      <c r="S296" s="4">
-        <v>4.584417285911032E-2</v>
-      </c>
-    </row>
-    <row r="297" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A297" s="2">
-        <v>9</v>
-      </c>
-      <c r="B297" s="2">
-        <v>9</v>
-      </c>
-      <c r="C297" s="2">
-        <v>0</v>
-      </c>
-      <c r="D297" s="2">
-        <v>5</v>
-      </c>
-      <c r="E297" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F297" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G297" s="2">
-        <v>78</v>
-      </c>
-      <c r="H297" s="2">
-        <v>11</v>
-      </c>
-      <c r="I297" s="2">
-        <v>67</v>
-      </c>
-      <c r="J297" s="4">
-        <v>0.18333333333333329</v>
-      </c>
-      <c r="K297" s="4">
-        <v>0.18484227510682361</v>
-      </c>
-      <c r="L297" s="4">
-        <v>0.16666666666666671</v>
-      </c>
-      <c r="M297" s="4">
-        <v>0.16666666666666671</v>
-      </c>
-      <c r="N297" s="4">
-        <v>0.20833333333333329</v>
-      </c>
-      <c r="O297" s="4">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="P297" s="4">
-        <v>0.3105387667887668</v>
-      </c>
-      <c r="Q297" s="4">
-        <v>0.14747677528381031</v>
-      </c>
-      <c r="R297" s="4">
-        <v>0.43162393162393159</v>
-      </c>
-      <c r="S297" s="4">
-        <v>8.9896085333173614E-2</v>
-      </c>
-    </row>
-    <row r="298" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A298" s="2">
-        <v>9</v>
-      </c>
-      <c r="B298" s="2">
-        <v>9</v>
-      </c>
-      <c r="C298" s="2">
-        <v>0</v>
-      </c>
-      <c r="D298" s="2">
-        <v>5</v>
-      </c>
-      <c r="E298" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F298" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G298" s="2">
-        <v>78</v>
-      </c>
-      <c r="H298" s="2">
-        <v>11</v>
-      </c>
-      <c r="I298" s="2">
-        <v>67</v>
-      </c>
-      <c r="J298" s="4">
-        <v>0.16666666666666671</v>
-      </c>
-      <c r="K298" s="4">
-        <v>0.28867513459481292</v>
-      </c>
-      <c r="L298" s="4">
-        <v>0.125</v>
-      </c>
-      <c r="M298" s="4">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="N298" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="O298" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="P298" s="4">
-        <v>0.39409305971805969</v>
-      </c>
-      <c r="Q298" s="4">
-        <v>0.34986908021491508</v>
-      </c>
-      <c r="R298" s="4">
-        <v>0.49252136752136749</v>
-      </c>
-      <c r="S298" s="4">
-        <v>0.29445925247767801</v>
-      </c>
-    </row>
-    <row r="299" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A299" s="2">
-        <v>9</v>
-      </c>
-      <c r="B299" s="2">
-        <v>9</v>
-      </c>
-      <c r="C299" s="2">
-        <v>0</v>
-      </c>
-      <c r="D299" s="2">
-        <v>5</v>
-      </c>
-      <c r="E299" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F299" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G299" s="2">
-        <v>78</v>
-      </c>
-      <c r="H299" s="2">
-        <v>11</v>
-      </c>
-      <c r="I299" s="2">
-        <v>67</v>
-      </c>
-      <c r="J299" s="4">
-        <v>0.28749999999999998</v>
-      </c>
-      <c r="K299" s="4">
-        <v>0.18833148966649199</v>
-      </c>
-      <c r="L299" s="4">
-        <v>0.21309523809523809</v>
-      </c>
-      <c r="M299" s="4">
-        <v>0.14813179000769669</v>
-      </c>
-      <c r="N299" s="4">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="O299" s="4">
-        <v>0.27322660517925001</v>
-      </c>
-      <c r="P299" s="4">
-        <v>0.31200396825396831</v>
-      </c>
-      <c r="Q299" s="4">
-        <v>7.5616911966063835E-2</v>
-      </c>
-      <c r="R299" s="4">
-        <v>0.7123397435897435</v>
-      </c>
-      <c r="S299" s="4">
-        <v>7.0380667244831843E-2</v>
-      </c>
-    </row>
-    <row r="300" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A300" s="2">
-        <v>9</v>
-      </c>
-      <c r="B300" s="2">
-        <v>9</v>
-      </c>
-      <c r="C300" s="2">
-        <v>0</v>
-      </c>
-      <c r="D300" s="2">
-        <v>5</v>
-      </c>
-      <c r="E300" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F300" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G300" s="2">
-        <v>78</v>
-      </c>
-      <c r="H300" s="2">
-        <v>11</v>
-      </c>
-      <c r="I300" s="2">
-        <v>67</v>
-      </c>
-      <c r="J300" s="4">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="K300" s="4">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="L300" s="4">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="M300" s="4">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="N300" s="4">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="O300" s="4">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="P300" s="4">
-        <v>0.32853835978835982</v>
-      </c>
-      <c r="Q300" s="4">
-        <v>8.8147376754867696E-2</v>
-      </c>
-      <c r="R300" s="4">
-        <v>0.68368437118437109</v>
-      </c>
-      <c r="S300" s="4">
-        <v>0.1068346360567254</v>
-      </c>
-    </row>
-    <row r="301" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A301" s="2">
-        <v>9</v>
-      </c>
-      <c r="B301" s="2">
-        <v>9</v>
-      </c>
-      <c r="C301" s="2">
-        <v>0</v>
-      </c>
-      <c r="D301" s="2">
-        <v>5</v>
-      </c>
-      <c r="E301" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F301" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G301" s="2">
-        <v>78</v>
-      </c>
-      <c r="H301" s="2">
-        <v>11</v>
-      </c>
-      <c r="I301" s="2">
-        <v>67</v>
-      </c>
-      <c r="J301" s="4">
-        <v>0.87857142857142856</v>
-      </c>
-      <c r="K301" s="4">
-        <v>7.388628880563286E-2</v>
-      </c>
-      <c r="L301" s="4">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="M301" s="4">
-        <v>0.125</v>
-      </c>
-      <c r="N301" s="4">
-        <v>1</v>
-      </c>
-      <c r="O301" s="4">
-        <v>0</v>
-      </c>
-      <c r="P301" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q301" s="4">
-        <v>0</v>
-      </c>
-      <c r="R301" s="4">
-        <v>1</v>
-      </c>
-      <c r="S301" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A302" s="2">
-        <v>9</v>
-      </c>
-      <c r="B302" s="2">
-        <v>9</v>
-      </c>
-      <c r="C302" s="2">
-        <v>0</v>
-      </c>
-      <c r="D302" s="2">
-        <v>5</v>
-      </c>
-      <c r="E302" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F302" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G302" s="2">
-        <v>78</v>
-      </c>
-      <c r="H302" s="2">
-        <v>11</v>
-      </c>
-      <c r="I302" s="2">
-        <v>67</v>
-      </c>
-      <c r="J302" s="4">
-        <v>1</v>
-      </c>
-      <c r="K302" s="4">
-        <v>0</v>
-      </c>
-      <c r="L302" s="4">
-        <v>1</v>
-      </c>
-      <c r="M302" s="4">
-        <v>0</v>
-      </c>
-      <c r="N302" s="4">
-        <v>1</v>
-      </c>
-      <c r="O302" s="4">
-        <v>0</v>
-      </c>
-      <c r="P302" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q302" s="4">
-        <v>0</v>
-      </c>
-      <c r="R302" s="4">
-        <v>1</v>
-      </c>
-      <c r="S302" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A303" s="2">
-        <v>9</v>
-      </c>
-      <c r="B303" s="2">
-        <v>9</v>
-      </c>
-      <c r="C303" s="2">
-        <v>0</v>
-      </c>
-      <c r="D303" s="2">
-        <v>5</v>
-      </c>
-      <c r="E303" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F303" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G303" s="2">
-        <v>78</v>
-      </c>
-      <c r="H303" s="2">
-        <v>11</v>
-      </c>
-      <c r="I303" s="2">
-        <v>67</v>
-      </c>
-      <c r="J303" s="4">
-        <v>1</v>
-      </c>
-      <c r="K303" s="4">
-        <v>0</v>
-      </c>
-      <c r="L303" s="4">
-        <v>1</v>
-      </c>
-      <c r="M303" s="4">
-        <v>0</v>
-      </c>
-      <c r="N303" s="4">
-        <v>1</v>
-      </c>
-      <c r="O303" s="4">
-        <v>0</v>
-      </c>
-      <c r="P303" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q303" s="4">
-        <v>0</v>
-      </c>
-      <c r="R303" s="4">
-        <v>1</v>
-      </c>
-      <c r="S303" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A304" s="2">
-        <v>9</v>
-      </c>
-      <c r="B304" s="2">
-        <v>9</v>
-      </c>
-      <c r="C304" s="2">
-        <v>0</v>
-      </c>
-      <c r="D304" s="2">
-        <v>5</v>
-      </c>
-      <c r="E304" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F304" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G304" s="2">
-        <v>78</v>
-      </c>
-      <c r="H304" s="2">
-        <v>11</v>
-      </c>
-      <c r="I304" s="2">
-        <v>67</v>
-      </c>
-      <c r="J304" s="4">
-        <v>1</v>
-      </c>
-      <c r="K304" s="4">
-        <v>0</v>
-      </c>
-      <c r="L304" s="4">
-        <v>1</v>
-      </c>
-      <c r="M304" s="4">
-        <v>0</v>
-      </c>
-      <c r="N304" s="4">
-        <v>1</v>
-      </c>
-      <c r="O304" s="4">
-        <v>0</v>
-      </c>
-      <c r="P304" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q304" s="4">
-        <v>0</v>
-      </c>
-      <c r="R304" s="4">
-        <v>1</v>
-      </c>
-      <c r="S304" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A305" s="2">
-        <v>9</v>
-      </c>
-      <c r="B305" s="2">
-        <v>9</v>
-      </c>
-      <c r="C305" s="2">
-        <v>0</v>
-      </c>
-      <c r="D305" s="2">
-        <v>5</v>
-      </c>
-      <c r="E305" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F305" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G305" s="2">
-        <v>78</v>
-      </c>
-      <c r="H305" s="2">
-        <v>11</v>
-      </c>
-      <c r="I305" s="2">
-        <v>67</v>
-      </c>
-      <c r="J305" s="4">
-        <v>0.95</v>
-      </c>
-      <c r="K305" s="4">
-        <v>8.6602540378443851E-2</v>
-      </c>
-      <c r="L305" s="4">
-        <v>1</v>
-      </c>
-      <c r="M305" s="4">
-        <v>0</v>
-      </c>
-      <c r="N305" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="O305" s="4">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="P305" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q305" s="4">
-        <v>0</v>
-      </c>
-      <c r="R305" s="4">
-        <v>1</v>
-      </c>
-      <c r="S305" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A306" s="2">
-        <v>9</v>
-      </c>
-      <c r="B306" s="2">
-        <v>9</v>
-      </c>
-      <c r="C306" s="2">
-        <v>0</v>
-      </c>
-      <c r="D306" s="2">
-        <v>5</v>
-      </c>
-      <c r="E306" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F306" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G306" s="2">
-        <v>78</v>
-      </c>
-      <c r="H306" s="2">
-        <v>11</v>
-      </c>
-      <c r="I306" s="2">
-        <v>67</v>
-      </c>
-      <c r="J306" s="4">
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="K306" s="4">
-        <v>7.1428571428571452E-2</v>
-      </c>
-      <c r="L306" s="4">
-        <v>0.875</v>
-      </c>
-      <c r="M306" s="4">
-        <v>0.125</v>
-      </c>
-      <c r="N306" s="4">
-        <v>1</v>
-      </c>
-      <c r="O306" s="4">
-        <v>0</v>
-      </c>
-      <c r="P306" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q306" s="4">
-        <v>0</v>
-      </c>
-      <c r="R306" s="4">
-        <v>1</v>
-      </c>
-      <c r="S306" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="307" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A307" s="2">
-        <v>9</v>
-      </c>
-      <c r="B307" s="2">
-        <v>9</v>
-      </c>
-      <c r="C307" s="2">
-        <v>0</v>
-      </c>
-      <c r="D307" s="2">
-        <v>5</v>
-      </c>
-      <c r="E307" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F307" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G307" s="2">
-        <v>78</v>
-      </c>
-      <c r="H307" s="2">
-        <v>11</v>
-      </c>
-      <c r="I307" s="2">
-        <v>67</v>
-      </c>
-      <c r="J307" s="4">
-        <v>1</v>
-      </c>
-      <c r="K307" s="4">
-        <v>0</v>
-      </c>
-      <c r="L307" s="4">
-        <v>1</v>
-      </c>
-      <c r="M307" s="4">
-        <v>0</v>
-      </c>
-      <c r="N307" s="4">
-        <v>1</v>
-      </c>
-      <c r="O307" s="4">
-        <v>0</v>
-      </c>
-      <c r="P307" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q307" s="4">
-        <v>0</v>
-      </c>
-      <c r="R307" s="4">
-        <v>1</v>
-      </c>
-      <c r="S307" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="308" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A308" s="2">
-        <v>9</v>
-      </c>
-      <c r="B308" s="2">
-        <v>9</v>
-      </c>
-      <c r="C308" s="2">
-        <v>0</v>
-      </c>
-      <c r="D308" s="2">
-        <v>5</v>
-      </c>
-      <c r="E308" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F308" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G308" s="2">
-        <v>78</v>
-      </c>
-      <c r="H308" s="2">
-        <v>11</v>
-      </c>
-      <c r="I308" s="2">
-        <v>67</v>
-      </c>
-      <c r="J308" s="4">
-        <v>1</v>
-      </c>
-      <c r="K308" s="4">
-        <v>0</v>
-      </c>
-      <c r="L308" s="4">
-        <v>1</v>
-      </c>
-      <c r="M308" s="4">
-        <v>0</v>
-      </c>
-      <c r="N308" s="4">
-        <v>1</v>
-      </c>
-      <c r="O308" s="4">
-        <v>0</v>
-      </c>
-      <c r="P308" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q308" s="4">
-        <v>0</v>
-      </c>
-      <c r="R308" s="4">
-        <v>1</v>
-      </c>
-      <c r="S308" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A309" s="2">
-        <v>9</v>
-      </c>
-      <c r="B309" s="2">
-        <v>9</v>
-      </c>
-      <c r="C309" s="2">
-        <v>0</v>
-      </c>
-      <c r="D309" s="2">
-        <v>5</v>
-      </c>
-      <c r="E309" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F309" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G309" s="2">
-        <v>78</v>
-      </c>
-      <c r="H309" s="2">
-        <v>11</v>
-      </c>
-      <c r="I309" s="2">
-        <v>67</v>
-      </c>
-      <c r="J309" s="4">
-        <v>0.91428571428571426</v>
-      </c>
-      <c r="K309" s="4">
-        <v>8.8063057185271076E-2</v>
-      </c>
-      <c r="L309" s="4">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="M309" s="4">
-        <v>0.14877975892797601</v>
-      </c>
-      <c r="N309" s="4">
-        <v>1</v>
-      </c>
-      <c r="O309" s="4">
-        <v>0</v>
-      </c>
-      <c r="P309" s="4">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="Q309" s="4">
-        <v>0.14877975892797601</v>
-      </c>
-      <c r="R309" s="4">
-        <v>0.98145604395604402</v>
-      </c>
-      <c r="S309" s="4">
-        <v>1.8569376146422761E-2</v>
-      </c>
-    </row>
-    <row r="310" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A310" s="2">
-        <v>9</v>
-      </c>
-      <c r="B310" s="2">
-        <v>9</v>
-      </c>
-      <c r="C310" s="2">
-        <v>0</v>
-      </c>
-      <c r="D310" s="2">
-        <v>5</v>
-      </c>
-      <c r="E310" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F310" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G310" s="2">
-        <v>78</v>
-      </c>
-      <c r="H310" s="2">
-        <v>11</v>
-      </c>
-      <c r="I310" s="2">
-        <v>67</v>
-      </c>
-      <c r="J310" s="4">
-        <v>0.95</v>
-      </c>
-      <c r="K310" s="4">
-        <v>8.6602540378443851E-2</v>
-      </c>
-      <c r="L310" s="4">
-        <v>1</v>
-      </c>
-      <c r="M310" s="4">
-        <v>0</v>
-      </c>
-      <c r="N310" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="O310" s="4">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="P310" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q310" s="4">
-        <v>0</v>
-      </c>
-      <c r="R310" s="4">
-        <v>1</v>
-      </c>
-      <c r="S310" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A311" s="2">
-        <v>9</v>
-      </c>
-      <c r="B311" s="2">
-        <v>9</v>
-      </c>
-      <c r="C311" s="2">
-        <v>0</v>
-      </c>
-      <c r="D311" s="2">
-        <v>5</v>
-      </c>
-      <c r="E311" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F311" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G311" s="2">
-        <v>78</v>
-      </c>
-      <c r="H311" s="2">
-        <v>11</v>
-      </c>
-      <c r="I311" s="2">
-        <v>67</v>
-      </c>
-      <c r="J311" s="4">
-        <v>0.87857142857142856</v>
-      </c>
-      <c r="K311" s="4">
-        <v>7.388628880563286E-2</v>
-      </c>
-      <c r="L311" s="4">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="M311" s="4">
-        <v>0.125</v>
-      </c>
-      <c r="N311" s="4">
-        <v>1</v>
-      </c>
-      <c r="O311" s="4">
-        <v>0</v>
-      </c>
-      <c r="P311" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q311" s="4">
-        <v>0</v>
-      </c>
-      <c r="R311" s="4">
-        <v>1</v>
-      </c>
-      <c r="S311" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="312" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A312" s="2">
-        <v>9</v>
-      </c>
-      <c r="B312" s="2">
-        <v>9</v>
-      </c>
-      <c r="C312" s="2">
-        <v>0</v>
-      </c>
-      <c r="D312" s="2">
-        <v>5</v>
-      </c>
-      <c r="E312" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F312" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G312" s="2">
-        <v>78</v>
-      </c>
-      <c r="H312" s="2">
-        <v>11</v>
-      </c>
-      <c r="I312" s="2">
-        <v>67</v>
-      </c>
-      <c r="J312" s="4">
-        <v>1</v>
-      </c>
-      <c r="K312" s="4">
-        <v>0</v>
-      </c>
-      <c r="L312" s="4">
-        <v>1</v>
-      </c>
-      <c r="M312" s="4">
-        <v>0</v>
-      </c>
-      <c r="N312" s="4">
-        <v>1</v>
-      </c>
-      <c r="O312" s="4">
-        <v>0</v>
-      </c>
-      <c r="P312" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q312" s="4">
-        <v>0</v>
-      </c>
-      <c r="R312" s="4">
-        <v>1</v>
-      </c>
-      <c r="S312" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="313" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A313" s="2">
-        <v>9</v>
-      </c>
-      <c r="B313" s="2">
-        <v>9</v>
-      </c>
-      <c r="C313" s="2">
-        <v>0</v>
-      </c>
-      <c r="D313" s="2">
-        <v>5</v>
-      </c>
-      <c r="E313" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F313" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G313" s="2">
-        <v>78</v>
-      </c>
-      <c r="H313" s="2">
-        <v>11</v>
-      </c>
-      <c r="I313" s="2">
-        <v>67</v>
-      </c>
-      <c r="J313" s="4">
-        <v>1</v>
-      </c>
-      <c r="K313" s="4">
-        <v>0</v>
-      </c>
-      <c r="L313" s="4">
-        <v>1</v>
-      </c>
-      <c r="M313" s="4">
-        <v>0</v>
-      </c>
-      <c r="N313" s="4">
-        <v>1</v>
-      </c>
-      <c r="O313" s="4">
-        <v>0</v>
-      </c>
-      <c r="P313" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q313" s="4">
-        <v>0</v>
-      </c>
-      <c r="R313" s="4">
-        <v>1</v>
-      </c>
-      <c r="S313" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="314" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A314" s="2">
-        <v>9</v>
-      </c>
-      <c r="B314" s="2">
-        <v>9</v>
-      </c>
-      <c r="C314" s="2">
-        <v>0</v>
-      </c>
-      <c r="D314" s="2">
-        <v>5</v>
-      </c>
-      <c r="E314" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F314" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G314" s="2">
-        <v>78</v>
-      </c>
-      <c r="H314" s="2">
-        <v>11</v>
-      </c>
-      <c r="I314" s="2">
-        <v>67</v>
-      </c>
-      <c r="J314" s="4">
-        <v>0.9642857142857143</v>
-      </c>
-      <c r="K314" s="4">
-        <v>6.1858957413174209E-2</v>
-      </c>
-      <c r="L314" s="4">
-        <v>0.9375</v>
-      </c>
-      <c r="M314" s="4">
-        <v>0.1082531754730548</v>
-      </c>
-      <c r="N314" s="4">
-        <v>1</v>
-      </c>
-      <c r="O314" s="4">
-        <v>0</v>
-      </c>
-      <c r="P314" s="4">
-        <v>0.9375</v>
-      </c>
-      <c r="Q314" s="4">
-        <v>0.1082531754730548</v>
-      </c>
-      <c r="R314" s="4">
-        <v>0.99038461538461542</v>
-      </c>
-      <c r="S314" s="4">
-        <v>1.665433468816227E-2</v>
-      </c>
-    </row>
-    <row r="315" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A315" s="2">
-        <v>9</v>
-      </c>
-      <c r="B315" s="2">
-        <v>9</v>
-      </c>
-      <c r="C315" s="2">
-        <v>0</v>
-      </c>
-      <c r="D315" s="2">
-        <v>5</v>
-      </c>
-      <c r="E315" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F315" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G315" s="2">
-        <v>78</v>
-      </c>
-      <c r="H315" s="2">
-        <v>11</v>
-      </c>
-      <c r="I315" s="2">
-        <v>67</v>
-      </c>
-      <c r="J315" s="4">
-        <v>0.95</v>
-      </c>
-      <c r="K315" s="4">
-        <v>8.6602540378443851E-2</v>
-      </c>
-      <c r="L315" s="4">
-        <v>1</v>
-      </c>
-      <c r="M315" s="4">
-        <v>0</v>
-      </c>
-      <c r="N315" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="O315" s="4">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="P315" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q315" s="4">
-        <v>0</v>
-      </c>
-      <c r="R315" s="4">
-        <v>1</v>
-      </c>
-      <c r="S315" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="316" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A316" s="2">
-        <v>9</v>
-      </c>
-      <c r="B316" s="2">
-        <v>9</v>
-      </c>
-      <c r="C316" s="2">
-        <v>0</v>
-      </c>
-      <c r="D316" s="2">
-        <v>5</v>
-      </c>
-      <c r="E316" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F316" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G316" s="2">
-        <v>78</v>
-      </c>
-      <c r="H316" s="2">
-        <v>11</v>
-      </c>
-      <c r="I316" s="2">
-        <v>67</v>
-      </c>
-      <c r="J316" s="4">
-        <v>0</v>
-      </c>
-      <c r="K316" s="4">
-        <v>0</v>
-      </c>
-      <c r="L316" s="4">
-        <v>0</v>
-      </c>
-      <c r="M316" s="4">
-        <v>0</v>
-      </c>
-      <c r="N316" s="4">
-        <v>0</v>
-      </c>
-      <c r="O316" s="4">
-        <v>0</v>
-      </c>
-      <c r="P316" s="4">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="Q316" s="4">
-        <v>2.9315098498896439E-2</v>
-      </c>
-      <c r="R316" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="S316" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="317" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A317" s="2">
-        <v>9</v>
-      </c>
-      <c r="B317" s="2">
-        <v>9</v>
-      </c>
-      <c r="C317" s="2">
-        <v>0</v>
-      </c>
-      <c r="D317" s="2">
-        <v>5</v>
-      </c>
-      <c r="E317" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F317" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G317" s="2">
-        <v>78</v>
-      </c>
-      <c r="H317" s="2">
-        <v>11</v>
-      </c>
-      <c r="I317" s="2">
-        <v>67</v>
-      </c>
-      <c r="J317" s="4">
-        <v>0.20833333333333329</v>
-      </c>
-      <c r="K317" s="4">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="L317" s="4">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="M317" s="4">
-        <v>0.40824829046386302</v>
-      </c>
-      <c r="N317" s="4">
-        <v>0.16666666666666671</v>
-      </c>
-      <c r="O317" s="4">
-        <v>0.16666666666666671</v>
-      </c>
-      <c r="P317" s="4">
-        <v>0.23784722222222221</v>
-      </c>
-      <c r="Q317" s="4">
-        <v>0.12566358059016541</v>
-      </c>
-      <c r="R317" s="4">
-        <v>0.42113095238095238</v>
-      </c>
-      <c r="S317" s="4">
-        <v>9.4806966882121882E-2</v>
-      </c>
-    </row>
-    <row r="318" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A318" s="2">
-        <v>9</v>
-      </c>
-      <c r="B318" s="2">
-        <v>9</v>
-      </c>
-      <c r="C318" s="2">
-        <v>0</v>
-      </c>
-      <c r="D318" s="2">
-        <v>5</v>
-      </c>
-      <c r="E318" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F318" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G318" s="2">
-        <v>78</v>
-      </c>
-      <c r="H318" s="2">
-        <v>11</v>
-      </c>
-      <c r="I318" s="2">
-        <v>67</v>
-      </c>
-      <c r="J318" s="4">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="K318" s="4">
-        <v>0.14433756729740641</v>
-      </c>
-      <c r="L318" s="4">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="M318" s="4">
-        <v>0.14433756729740641</v>
-      </c>
-      <c r="N318" s="4">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="O318" s="4">
-        <v>0.14433756729740641</v>
-      </c>
-      <c r="P318" s="4">
-        <v>0.17539682539682541</v>
-      </c>
-      <c r="Q318" s="4">
-        <v>6.8214303027782516E-2</v>
-      </c>
-      <c r="R318" s="4">
-        <v>0.35367063492063489</v>
-      </c>
-      <c r="S318" s="4">
-        <v>0.12954978020007071</v>
-      </c>
-    </row>
-    <row r="319" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A319" s="2">
-        <v>9</v>
-      </c>
-      <c r="B319" s="2">
-        <v>9</v>
-      </c>
-      <c r="C319" s="2">
-        <v>0</v>
-      </c>
-      <c r="D319" s="2">
-        <v>5</v>
-      </c>
-      <c r="E319" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F319" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G319" s="2">
-        <v>78</v>
-      </c>
-      <c r="H319" s="2">
-        <v>11</v>
-      </c>
-      <c r="I319" s="2">
-        <v>67</v>
-      </c>
-      <c r="J319" s="4">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="K319" s="4">
-        <v>0.14433756729740641</v>
-      </c>
-      <c r="L319" s="4">
-        <v>0.05</v>
-      </c>
-      <c r="M319" s="4">
-        <v>8.6602540378443879E-2</v>
-      </c>
-      <c r="N319" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="O319" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="P319" s="4">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="Q319" s="4">
-        <v>2.9315098498896439E-2</v>
-      </c>
-      <c r="R319" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="S319" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="320" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A320" s="2">
-        <v>9</v>
-      </c>
-      <c r="B320" s="2">
-        <v>9</v>
-      </c>
-      <c r="C320" s="2">
-        <v>0</v>
-      </c>
-      <c r="D320" s="2">
-        <v>5</v>
-      </c>
-      <c r="E320" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F320" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G320" s="2">
-        <v>78</v>
-      </c>
-      <c r="H320" s="2">
-        <v>11</v>
-      </c>
-      <c r="I320" s="2">
-        <v>67</v>
-      </c>
-      <c r="J320" s="4">
-        <v>0.46785714285714292</v>
-      </c>
-      <c r="K320" s="4">
-        <v>0.29196292048610473</v>
-      </c>
-      <c r="L320" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="M320" s="4">
-        <v>0.35355339059327379</v>
-      </c>
-      <c r="N320" s="4">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="O320" s="4">
-        <v>0.27322660517925001</v>
-      </c>
-      <c r="P320" s="4">
-        <v>0.39340277777777782</v>
-      </c>
-      <c r="Q320" s="4">
-        <v>0.2025311832986055</v>
-      </c>
-      <c r="R320" s="4">
-        <v>0.68898809523809512</v>
-      </c>
-      <c r="S320" s="4">
-        <v>0.11996484450551979</v>
-      </c>
-    </row>
-    <row r="321" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A321" s="2">
-        <v>9</v>
-      </c>
-      <c r="B321" s="2">
-        <v>9</v>
-      </c>
-      <c r="C321" s="2">
-        <v>0</v>
-      </c>
-      <c r="D321" s="2">
-        <v>5</v>
-      </c>
-      <c r="E321" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F321" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G321" s="2">
-        <v>78</v>
-      </c>
-      <c r="H321" s="2">
-        <v>11</v>
-      </c>
-      <c r="I321" s="2">
-        <v>67</v>
-      </c>
-      <c r="J321" s="4">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="K321" s="4">
-        <v>0.1020620726159658</v>
-      </c>
-      <c r="L321" s="4">
-        <v>0.27500000000000002</v>
-      </c>
-      <c r="M321" s="4">
-        <v>9.5379359518829976E-2</v>
-      </c>
-      <c r="N321" s="4">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="O321" s="4">
-        <v>0.13819269959814159</v>
-      </c>
-      <c r="P321" s="4">
-        <v>0.54662698412698407</v>
-      </c>
-      <c r="Q321" s="4">
-        <v>0.19066469260536631</v>
-      </c>
-      <c r="R321" s="4">
-        <v>0.79296398046398042</v>
-      </c>
-      <c r="S321" s="4">
-        <v>7.1949243665153442E-2</v>
-      </c>
-    </row>
-    <row r="322" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A322" s="2">
-        <v>9</v>
-      </c>
-      <c r="B322" s="2">
-        <v>9</v>
-      </c>
-      <c r="C322" s="2">
-        <v>0</v>
-      </c>
-      <c r="D322" s="2">
-        <v>5</v>
-      </c>
-      <c r="E322" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F322" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G322" s="2">
-        <v>78</v>
-      </c>
-      <c r="H322" s="2">
-        <v>11</v>
-      </c>
-      <c r="I322" s="2">
-        <v>67</v>
-      </c>
-      <c r="J322" s="4">
-        <v>0.3214285714285714</v>
-      </c>
-      <c r="K322" s="4">
-        <v>0.1041241409793804</v>
-      </c>
-      <c r="L322" s="4">
-        <v>0.24583333333333329</v>
-      </c>
-      <c r="M322" s="4">
-        <v>5.4486236794258409E-2</v>
-      </c>
-      <c r="N322" s="4">
-        <v>0.49999999999999989</v>
-      </c>
-      <c r="O322" s="4">
-        <v>0.28867513459481292</v>
-      </c>
-      <c r="P322" s="4">
-        <v>0.46755952380952381</v>
-      </c>
-      <c r="Q322" s="4">
-        <v>0.30954140861139201</v>
-      </c>
-      <c r="R322" s="4">
-        <v>0.64476495726495719</v>
-      </c>
-      <c r="S322" s="4">
-        <v>0.22805450049045589</v>
-      </c>
-    </row>
-    <row r="323" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A323" s="2">
-        <v>9</v>
-      </c>
-      <c r="B323" s="2">
-        <v>9</v>
-      </c>
-      <c r="C323" s="2">
-        <v>0</v>
-      </c>
-      <c r="D323" s="2">
-        <v>5</v>
-      </c>
-      <c r="E323" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F323" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G323" s="2">
-        <v>78</v>
-      </c>
-      <c r="H323" s="2">
-        <v>11</v>
-      </c>
-      <c r="I323" s="2">
-        <v>67</v>
-      </c>
-      <c r="J323" s="4">
-        <v>0.35119047619047622</v>
-      </c>
-      <c r="K323" s="4">
-        <v>8.8087193969932989E-2</v>
-      </c>
-      <c r="L323" s="4">
-        <v>0.29166666666666657</v>
-      </c>
-      <c r="M323" s="4">
-        <v>4.1666666666666657E-2</v>
-      </c>
-      <c r="N323" s="4">
-        <v>0.49999999999999989</v>
-      </c>
-      <c r="O323" s="4">
-        <v>0.28867513459481292</v>
-      </c>
-      <c r="P323" s="4">
-        <v>0.44231913919413912</v>
-      </c>
-      <c r="Q323" s="4">
-        <v>0.32277170080521272</v>
-      </c>
-      <c r="R323" s="4">
-        <v>0.55822649572649574</v>
-      </c>
-      <c r="S323" s="4">
-        <v>0.26692034952258969</v>
-      </c>
-    </row>
-    <row r="324" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A324" s="2">
-        <v>9</v>
-      </c>
-      <c r="B324" s="2">
-        <v>9</v>
-      </c>
-      <c r="C324" s="2">
-        <v>0</v>
-      </c>
-      <c r="D324" s="2">
-        <v>5</v>
-      </c>
-      <c r="E324" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F324" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G324" s="2">
-        <v>78</v>
-      </c>
-      <c r="H324" s="2">
-        <v>11</v>
-      </c>
-      <c r="I324" s="2">
-        <v>67</v>
-      </c>
-      <c r="J324" s="4">
-        <v>0.28749999999999998</v>
-      </c>
-      <c r="K324" s="4">
-        <v>0.18833148966649199</v>
-      </c>
-      <c r="L324" s="4">
-        <v>0.21309523809523809</v>
-      </c>
-      <c r="M324" s="4">
-        <v>0.14813179000769669</v>
-      </c>
-      <c r="N324" s="4">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="O324" s="4">
-        <v>0.27322660517925001</v>
-      </c>
-      <c r="P324" s="4">
-        <v>0.31200396825396831</v>
-      </c>
-      <c r="Q324" s="4">
-        <v>7.5616911966063835E-2</v>
-      </c>
-      <c r="R324" s="4">
-        <v>0.7123397435897435</v>
-      </c>
-      <c r="S324" s="4">
-        <v>7.0380667244831843E-2</v>
-      </c>
-    </row>
-    <row r="325" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A325" s="2">
-        <v>9</v>
-      </c>
-      <c r="B325" s="2">
-        <v>9</v>
-      </c>
-      <c r="C325" s="2">
-        <v>0</v>
-      </c>
-      <c r="D325" s="2">
-        <v>5</v>
-      </c>
-      <c r="E325" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F325" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G325" s="2">
-        <v>78</v>
-      </c>
-      <c r="H325" s="2">
-        <v>11</v>
-      </c>
-      <c r="I325" s="2">
-        <v>67</v>
-      </c>
-      <c r="J325" s="4">
-        <v>0</v>
-      </c>
-      <c r="K325" s="4">
-        <v>0</v>
-      </c>
-      <c r="L325" s="4">
-        <v>0</v>
-      </c>
-      <c r="M325" s="4">
-        <v>0</v>
-      </c>
-      <c r="N325" s="4">
-        <v>0</v>
-      </c>
-      <c r="O325" s="4">
-        <v>0</v>
-      </c>
-      <c r="P325" s="4">
-        <v>0.29771201021201021</v>
-      </c>
-      <c r="Q325" s="4">
-        <v>9.3269238633410217E-2</v>
-      </c>
-      <c r="R325" s="4">
-        <v>0.60645604395604391</v>
-      </c>
-      <c r="S325" s="4">
-        <v>0.13292018866004571</v>
-      </c>
-    </row>
-    <row r="326" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A326" s="2">
-        <v>10</v>
-      </c>
-      <c r="B326" s="2">
-        <v>10</v>
-      </c>
-      <c r="C326" s="2">
-        <v>0</v>
-      </c>
-      <c r="D326" s="2">
-        <v>5</v>
-      </c>
-      <c r="E326" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F326" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G326" s="2">
-        <v>33</v>
-      </c>
-      <c r="H326" s="2">
-        <v>8</v>
-      </c>
-      <c r="I326" s="2">
-        <v>25</v>
-      </c>
-      <c r="J326" s="4">
-        <v>0.44861111111111113</v>
-      </c>
-      <c r="K326" s="4">
-        <v>0.12749818444604241</v>
-      </c>
-      <c r="L326" s="4">
-        <v>0.29761904761904762</v>
-      </c>
-      <c r="M326" s="4">
-        <v>0.10309826235529029</v>
-      </c>
-      <c r="N326" s="4">
-        <v>1</v>
-      </c>
-      <c r="O326" s="4">
-        <v>0</v>
-      </c>
-      <c r="P326" s="4">
-        <v>0.29761904761904762</v>
-      </c>
-      <c r="Q326" s="4">
-        <v>0.10309826235529029</v>
-      </c>
-      <c r="R326" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="S326" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A327" s="2">
-        <v>10</v>
-      </c>
-      <c r="B327" s="2">
-        <v>10</v>
-      </c>
-      <c r="C327" s="2">
-        <v>0</v>
-      </c>
-      <c r="D327" s="2">
-        <v>5</v>
-      </c>
-      <c r="E327" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F327" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G327" s="2">
-        <v>33</v>
-      </c>
-      <c r="H327" s="2">
-        <v>8</v>
-      </c>
-      <c r="I327" s="2">
-        <v>25</v>
-      </c>
-      <c r="J327" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="K327" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="L327" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="M327" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="N327" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="O327" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="P327" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q327" s="4">
-        <v>0</v>
-      </c>
-      <c r="R327" s="4">
-        <v>1</v>
-      </c>
-      <c r="S327" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A328" s="2">
-        <v>10</v>
-      </c>
-      <c r="B328" s="2">
-        <v>10</v>
-      </c>
-      <c r="C328" s="2">
-        <v>0</v>
-      </c>
-      <c r="D328" s="2">
-        <v>5</v>
-      </c>
-      <c r="E328" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F328" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G328" s="2">
-        <v>33</v>
-      </c>
-      <c r="H328" s="2">
-        <v>8</v>
-      </c>
-      <c r="I328" s="2">
-        <v>25</v>
-      </c>
-      <c r="J328" s="4">
-        <v>0.95</v>
-      </c>
-      <c r="K328" s="4">
-        <v>8.6602540378443851E-2</v>
-      </c>
-      <c r="L328" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="M328" s="4">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="N328" s="4">
-        <v>1</v>
-      </c>
-      <c r="O328" s="4">
-        <v>0</v>
-      </c>
-      <c r="P328" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q328" s="4">
-        <v>0</v>
-      </c>
-      <c r="R328" s="4">
-        <v>1</v>
-      </c>
-      <c r="S328" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A329" s="2">
-        <v>10</v>
-      </c>
-      <c r="B329" s="2">
-        <v>10</v>
-      </c>
-      <c r="C329" s="2">
-        <v>0</v>
-      </c>
-      <c r="D329" s="2">
-        <v>5</v>
-      </c>
-      <c r="E329" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F329" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G329" s="2">
-        <v>33</v>
-      </c>
-      <c r="H329" s="2">
-        <v>8</v>
-      </c>
-      <c r="I329" s="2">
-        <v>25</v>
-      </c>
-      <c r="J329" s="4">
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="K329" s="4">
-        <v>9.9999999999999978E-2</v>
-      </c>
-      <c r="L329" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="M329" s="4">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="N329" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="O329" s="4">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="P329" s="4">
-        <v>0.97916666666666663</v>
-      </c>
-      <c r="Q329" s="4">
-        <v>3.6084391824351678E-2</v>
-      </c>
-      <c r="R329" s="4">
-        <v>0.97916666666666663</v>
-      </c>
-      <c r="S329" s="4">
-        <v>3.6084391824351629E-2</v>
-      </c>
-    </row>
-    <row r="330" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A330" s="2">
-        <v>10</v>
-      </c>
-      <c r="B330" s="2">
-        <v>10</v>
-      </c>
-      <c r="C330" s="2">
-        <v>0</v>
-      </c>
-      <c r="D330" s="2">
-        <v>5</v>
-      </c>
-      <c r="E330" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F330" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G330" s="2">
-        <v>33</v>
-      </c>
-      <c r="H330" s="2">
-        <v>8</v>
-      </c>
-      <c r="I330" s="2">
-        <v>25</v>
-      </c>
-      <c r="J330" s="4">
-        <v>0.8666666666666667</v>
-      </c>
-      <c r="K330" s="4">
-        <v>0.1414213562373095</v>
-      </c>
-      <c r="L330" s="4">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="M330" s="4">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="N330" s="4">
-        <v>1</v>
-      </c>
-      <c r="O330" s="4">
-        <v>0</v>
-      </c>
-      <c r="P330" s="4">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="Q330" s="4">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="R330" s="4">
-        <v>0.94791666666666674</v>
-      </c>
-      <c r="S330" s="4">
-        <v>5.4126587736527412E-2</v>
-      </c>
-    </row>
-    <row r="331" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A331" s="2">
-        <v>10</v>
-      </c>
-      <c r="B331" s="2">
-        <v>10</v>
-      </c>
-      <c r="C331" s="2">
-        <v>0</v>
-      </c>
-      <c r="D331" s="2">
-        <v>5</v>
-      </c>
-      <c r="E331" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F331" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G331" s="2">
-        <v>33</v>
-      </c>
-      <c r="H331" s="2">
-        <v>8</v>
-      </c>
-      <c r="I331" s="2">
-        <v>25</v>
-      </c>
-      <c r="J331" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="K331" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="L331" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="M331" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="N331" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="O331" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="P331" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q331" s="4">
-        <v>0</v>
-      </c>
-      <c r="R331" s="4">
-        <v>1</v>
-      </c>
-      <c r="S331" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A332" s="2">
-        <v>10</v>
-      </c>
-      <c r="B332" s="2">
-        <v>10</v>
-      </c>
-      <c r="C332" s="2">
-        <v>0</v>
-      </c>
-      <c r="D332" s="2">
-        <v>5</v>
-      </c>
-      <c r="E332" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F332" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G332" s="2">
-        <v>33</v>
-      </c>
-      <c r="H332" s="2">
-        <v>8</v>
-      </c>
-      <c r="I332" s="2">
-        <v>25</v>
-      </c>
-      <c r="J332" s="4">
-        <v>0</v>
-      </c>
-      <c r="K332" s="4">
-        <v>0</v>
-      </c>
-      <c r="L332" s="4">
-        <v>0</v>
-      </c>
-      <c r="M332" s="4">
-        <v>0</v>
-      </c>
-      <c r="N332" s="4">
-        <v>0</v>
-      </c>
-      <c r="O332" s="4">
-        <v>0</v>
-      </c>
-      <c r="P332" s="4">
-        <v>0.70138888888888884</v>
-      </c>
-      <c r="Q332" s="4">
-        <v>0.17388866702151271</v>
-      </c>
-      <c r="R332" s="4">
-        <v>0.83750000000000002</v>
-      </c>
-      <c r="S332" s="4">
-        <v>0.1023169096484056</v>
-      </c>
-    </row>
-    <row r="333" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A333" s="2">
-        <v>10</v>
-      </c>
-      <c r="B333" s="2">
-        <v>10</v>
-      </c>
-      <c r="C333" s="2">
-        <v>0</v>
-      </c>
-      <c r="D333" s="2">
-        <v>5</v>
-      </c>
-      <c r="E333" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F333" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G333" s="2">
-        <v>33</v>
-      </c>
-      <c r="H333" s="2">
-        <v>8</v>
-      </c>
-      <c r="I333" s="2">
-        <v>25</v>
-      </c>
-      <c r="J333" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="K333" s="4">
-        <v>0.17320508075688781</v>
-      </c>
-      <c r="L333" s="4">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="M333" s="4">
-        <v>0.14433756729740641</v>
-      </c>
-      <c r="N333" s="4">
-        <v>0.125</v>
-      </c>
-      <c r="O333" s="4">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="P333" s="4">
-        <v>0.46418650793650801</v>
-      </c>
-      <c r="Q333" s="4">
-        <v>0.19461653685934091</v>
-      </c>
-      <c r="R333" s="4">
-        <v>0.53749999999999998</v>
-      </c>
-      <c r="S333" s="4">
-        <v>0.12930100540985751</v>
-      </c>
-    </row>
-    <row r="334" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A334" s="2">
-        <v>10</v>
-      </c>
-      <c r="B334" s="2">
-        <v>10</v>
-      </c>
-      <c r="C334" s="2">
-        <v>0</v>
-      </c>
-      <c r="D334" s="2">
-        <v>5</v>
-      </c>
-      <c r="E334" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F334" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G334" s="2">
-        <v>33</v>
-      </c>
-      <c r="H334" s="2">
-        <v>8</v>
-      </c>
-      <c r="I334" s="2">
-        <v>25</v>
-      </c>
-      <c r="J334" s="4">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="K334" s="4">
-        <v>0.14433756729740641</v>
-      </c>
-      <c r="L334" s="4">
-        <v>6.25E-2</v>
-      </c>
-      <c r="M334" s="4">
-        <v>0.1082531754730548</v>
-      </c>
-      <c r="N334" s="4">
-        <v>0.125</v>
-      </c>
-      <c r="O334" s="4">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="P334" s="4">
-        <v>0.42946428571428569</v>
-      </c>
-      <c r="Q334" s="4">
-        <v>0.1778823510375821</v>
-      </c>
-      <c r="R334" s="4">
-        <v>0.46041666666666659</v>
-      </c>
-      <c r="S334" s="4">
-        <v>0.11864030020753211</v>
-      </c>
-    </row>
-    <row r="335" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A335" s="2">
-        <v>10</v>
-      </c>
-      <c r="B335" s="2">
-        <v>10</v>
-      </c>
-      <c r="C335" s="2">
-        <v>0</v>
-      </c>
-      <c r="D335" s="2">
-        <v>5</v>
-      </c>
-      <c r="E335" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F335" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G335" s="2">
-        <v>33</v>
-      </c>
-      <c r="H335" s="2">
-        <v>8</v>
-      </c>
-      <c r="I335" s="2">
-        <v>25</v>
-      </c>
-      <c r="J335" s="4">
-        <v>0.63452380952380949</v>
-      </c>
-      <c r="K335" s="4">
-        <v>0.11235345708845761</v>
-      </c>
-      <c r="L335" s="4">
-        <v>0.51666666666666661</v>
-      </c>
-      <c r="M335" s="4">
-        <v>0.15184055965240489</v>
-      </c>
-      <c r="N335" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="O335" s="4">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="P335" s="4">
-        <v>0.49682539682539678</v>
-      </c>
-      <c r="Q335" s="4">
-        <v>0.13521909099648929</v>
-      </c>
-      <c r="R335" s="4">
-        <v>0.76666666666666672</v>
-      </c>
-      <c r="S335" s="4">
-        <v>0.1068812944865055</v>
-      </c>
-    </row>
-    <row r="336" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A336" s="2">
-        <v>10</v>
-      </c>
-      <c r="B336" s="2">
-        <v>10</v>
-      </c>
-      <c r="C336" s="2">
-        <v>0</v>
-      </c>
-      <c r="D336" s="2">
-        <v>5</v>
-      </c>
-      <c r="E336" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F336" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G336" s="2">
-        <v>33</v>
-      </c>
-      <c r="H336" s="2">
-        <v>8</v>
-      </c>
-      <c r="I336" s="2">
-        <v>25</v>
-      </c>
-      <c r="J336" s="4">
-        <v>0.22500000000000001</v>
-      </c>
-      <c r="K336" s="4">
-        <v>0.22776083947860751</v>
-      </c>
-      <c r="L336" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="M336" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="N336" s="4">
-        <v>0.20833333333333329</v>
-      </c>
-      <c r="O336" s="4">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="P336" s="4">
-        <v>0.53363095238095237</v>
-      </c>
-      <c r="Q336" s="4">
-        <v>0.21528927534946751</v>
-      </c>
-      <c r="R336" s="4">
-        <v>0.57916666666666661</v>
-      </c>
-      <c r="S336" s="4">
-        <v>0.2372806004150641</v>
-      </c>
-    </row>
-    <row r="337" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A337" s="2">
-        <v>10</v>
-      </c>
-      <c r="B337" s="2">
-        <v>10</v>
-      </c>
-      <c r="C337" s="2">
-        <v>0</v>
-      </c>
-      <c r="D337" s="2">
-        <v>5</v>
-      </c>
-      <c r="E337" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F337" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G337" s="2">
-        <v>33</v>
-      </c>
-      <c r="H337" s="2">
-        <v>8</v>
-      </c>
-      <c r="I337" s="2">
-        <v>25</v>
-      </c>
-      <c r="J337" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="K337" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="L337" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="M337" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="N337" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="O337" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="P337" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q337" s="4">
-        <v>0</v>
-      </c>
-      <c r="R337" s="4">
-        <v>1</v>
-      </c>
-      <c r="S337" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="338" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A338" s="2">
-        <v>10</v>
-      </c>
-      <c r="B338" s="2">
-        <v>10</v>
-      </c>
-      <c r="C338" s="2">
-        <v>0</v>
-      </c>
-      <c r="D338" s="2">
-        <v>5</v>
-      </c>
-      <c r="E338" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F338" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G338" s="2">
-        <v>33</v>
-      </c>
-      <c r="H338" s="2">
-        <v>8</v>
-      </c>
-      <c r="I338" s="2">
-        <v>25</v>
-      </c>
-      <c r="J338" s="4">
-        <v>0.95</v>
-      </c>
-      <c r="K338" s="4">
-        <v>8.6602540378443851E-2</v>
-      </c>
-      <c r="L338" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="M338" s="4">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="N338" s="4">
-        <v>1</v>
-      </c>
-      <c r="O338" s="4">
-        <v>0</v>
-      </c>
-      <c r="P338" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q338" s="4">
-        <v>0</v>
-      </c>
-      <c r="R338" s="4">
-        <v>1</v>
-      </c>
-      <c r="S338" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="339" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A339" s="2">
-        <v>10</v>
-      </c>
-      <c r="B339" s="2">
-        <v>10</v>
-      </c>
-      <c r="C339" s="2">
-        <v>0</v>
-      </c>
-      <c r="D339" s="2">
-        <v>5</v>
-      </c>
-      <c r="E339" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F339" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G339" s="2">
-        <v>33</v>
-      </c>
-      <c r="H339" s="2">
-        <v>8</v>
-      </c>
-      <c r="I339" s="2">
-        <v>25</v>
-      </c>
-      <c r="J339" s="4">
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="K339" s="4">
-        <v>9.9999999999999978E-2</v>
-      </c>
-      <c r="L339" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="M339" s="4">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="N339" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="O339" s="4">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="P339" s="4">
-        <v>0.97916666666666663</v>
-      </c>
-      <c r="Q339" s="4">
-        <v>3.6084391824351678E-2</v>
-      </c>
-      <c r="R339" s="4">
-        <v>0.97916666666666663</v>
-      </c>
-      <c r="S339" s="4">
-        <v>3.6084391824351629E-2</v>
-      </c>
-    </row>
-    <row r="340" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A340" s="2">
-        <v>10</v>
-      </c>
-      <c r="B340" s="2">
-        <v>10</v>
-      </c>
-      <c r="C340" s="2">
-        <v>0</v>
-      </c>
-      <c r="D340" s="2">
-        <v>5</v>
-      </c>
-      <c r="E340" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F340" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G340" s="2">
-        <v>33</v>
-      </c>
-      <c r="H340" s="2">
-        <v>8</v>
-      </c>
-      <c r="I340" s="2">
-        <v>25</v>
-      </c>
-      <c r="J340" s="4">
-        <v>0.83095238095238089</v>
-      </c>
-      <c r="K340" s="4">
-        <v>0.1195939843321368</v>
-      </c>
-      <c r="L340" s="4">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="M340" s="4">
-        <v>0.18042195912175801</v>
-      </c>
-      <c r="N340" s="4">
-        <v>1</v>
-      </c>
-      <c r="O340" s="4">
-        <v>0</v>
-      </c>
-      <c r="P340" s="4">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="Q340" s="4">
-        <v>0.18042195912175801</v>
-      </c>
-      <c r="R340" s="4">
-        <v>0.88749999999999996</v>
-      </c>
-      <c r="S340" s="4">
-        <v>7.1807033081725341E-2</v>
-      </c>
-    </row>
-    <row r="341" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A341" s="2">
-        <v>10</v>
-      </c>
-      <c r="B341" s="2">
-        <v>10</v>
-      </c>
-      <c r="C341" s="2">
-        <v>0</v>
-      </c>
-      <c r="D341" s="2">
-        <v>5</v>
-      </c>
-      <c r="E341" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F341" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G341" s="2">
-        <v>33</v>
-      </c>
-      <c r="H341" s="2">
-        <v>8</v>
-      </c>
-      <c r="I341" s="2">
-        <v>25</v>
-      </c>
-      <c r="J341" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="K341" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="L341" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="M341" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="N341" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="O341" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="P341" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q341" s="4">
-        <v>0</v>
-      </c>
-      <c r="R341" s="4">
-        <v>1</v>
-      </c>
-      <c r="S341" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="342" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A342" s="2">
-        <v>10</v>
-      </c>
-      <c r="B342" s="2">
-        <v>10</v>
-      </c>
-      <c r="C342" s="2">
-        <v>0</v>
-      </c>
-      <c r="D342" s="2">
-        <v>5</v>
-      </c>
-      <c r="E342" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F342" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G342" s="2">
-        <v>33</v>
-      </c>
-      <c r="H342" s="2">
-        <v>8</v>
-      </c>
-      <c r="I342" s="2">
-        <v>25</v>
-      </c>
-      <c r="J342" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="K342" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="L342" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="M342" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="N342" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="O342" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="P342" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q342" s="4">
-        <v>0</v>
-      </c>
-      <c r="R342" s="4">
-        <v>1</v>
-      </c>
-      <c r="S342" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="343" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A343" s="2">
-        <v>10</v>
-      </c>
-      <c r="B343" s="2">
-        <v>10</v>
-      </c>
-      <c r="C343" s="2">
-        <v>0</v>
-      </c>
-      <c r="D343" s="2">
-        <v>5</v>
-      </c>
-      <c r="E343" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F343" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G343" s="2">
-        <v>33</v>
-      </c>
-      <c r="H343" s="2">
-        <v>8</v>
-      </c>
-      <c r="I343" s="2">
-        <v>25</v>
-      </c>
-      <c r="J343" s="4">
-        <v>0.95</v>
-      </c>
-      <c r="K343" s="4">
-        <v>8.6602540378443851E-2</v>
-      </c>
-      <c r="L343" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="M343" s="4">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="N343" s="4">
-        <v>1</v>
-      </c>
-      <c r="O343" s="4">
-        <v>0</v>
-      </c>
-      <c r="P343" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q343" s="4">
-        <v>0</v>
-      </c>
-      <c r="R343" s="4">
-        <v>1</v>
-      </c>
-      <c r="S343" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="344" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A344" s="2">
-        <v>10</v>
-      </c>
-      <c r="B344" s="2">
-        <v>10</v>
-      </c>
-      <c r="C344" s="2">
-        <v>0</v>
-      </c>
-      <c r="D344" s="2">
-        <v>5</v>
-      </c>
-      <c r="E344" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F344" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G344" s="2">
-        <v>33</v>
-      </c>
-      <c r="H344" s="2">
-        <v>8</v>
-      </c>
-      <c r="I344" s="2">
-        <v>25</v>
-      </c>
-      <c r="J344" s="4">
-        <v>0.95</v>
-      </c>
-      <c r="K344" s="4">
-        <v>8.6602540378443851E-2</v>
-      </c>
-      <c r="L344" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="M344" s="4">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="N344" s="4">
-        <v>1</v>
-      </c>
-      <c r="O344" s="4">
-        <v>0</v>
-      </c>
-      <c r="P344" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q344" s="4">
-        <v>0</v>
-      </c>
-      <c r="R344" s="4">
-        <v>1</v>
-      </c>
-      <c r="S344" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="345" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A345" s="2">
-        <v>10</v>
-      </c>
-      <c r="B345" s="2">
-        <v>10</v>
-      </c>
-      <c r="C345" s="2">
-        <v>0</v>
-      </c>
-      <c r="D345" s="2">
-        <v>5</v>
-      </c>
-      <c r="E345" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F345" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G345" s="2">
-        <v>33</v>
-      </c>
-      <c r="H345" s="2">
-        <v>8</v>
-      </c>
-      <c r="I345" s="2">
-        <v>25</v>
-      </c>
-      <c r="J345" s="4">
-        <v>0.82499999999999996</v>
-      </c>
-      <c r="K345" s="4">
-        <v>0.20463381929681121</v>
-      </c>
-      <c r="L345" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="M345" s="4">
-        <v>0.27638539919628341</v>
-      </c>
-      <c r="N345" s="4">
-        <v>1</v>
-      </c>
-      <c r="O345" s="4">
-        <v>0</v>
-      </c>
-      <c r="P345" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="Q345" s="4">
-        <v>0.27638539919628341</v>
-      </c>
-      <c r="R345" s="4">
-        <v>0.92708333333333337</v>
-      </c>
-      <c r="S345" s="4">
-        <v>7.4389879463988007E-2</v>
-      </c>
-    </row>
-    <row r="346" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A346" s="2">
-        <v>10</v>
-      </c>
-      <c r="B346" s="2">
-        <v>10</v>
-      </c>
-      <c r="C346" s="2">
-        <v>0</v>
-      </c>
-      <c r="D346" s="2">
-        <v>5</v>
-      </c>
-      <c r="E346" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F346" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G346" s="2">
-        <v>33</v>
-      </c>
-      <c r="H346" s="2">
-        <v>8</v>
-      </c>
-      <c r="I346" s="2">
-        <v>25</v>
-      </c>
-      <c r="J346" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="K346" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="L346" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="M346" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="N346" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="O346" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="P346" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q346" s="4">
-        <v>0</v>
-      </c>
-      <c r="R346" s="4">
-        <v>1</v>
-      </c>
-      <c r="S346" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="347" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A347" s="2">
-        <v>10</v>
-      </c>
-      <c r="B347" s="2">
-        <v>10</v>
-      </c>
-      <c r="C347" s="2">
-        <v>0</v>
-      </c>
-      <c r="D347" s="2">
-        <v>5</v>
-      </c>
-      <c r="E347" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F347" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G347" s="2">
-        <v>33</v>
-      </c>
-      <c r="H347" s="2">
-        <v>8</v>
-      </c>
-      <c r="I347" s="2">
-        <v>25</v>
-      </c>
-      <c r="J347" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="K347" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="L347" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="M347" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="N347" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="O347" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="P347" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q347" s="4">
-        <v>0</v>
-      </c>
-      <c r="R347" s="4">
-        <v>1</v>
-      </c>
-      <c r="S347" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="348" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A348" s="2">
-        <v>10</v>
-      </c>
-      <c r="B348" s="2">
-        <v>10</v>
-      </c>
-      <c r="C348" s="2">
-        <v>0</v>
-      </c>
-      <c r="D348" s="2">
-        <v>5</v>
-      </c>
-      <c r="E348" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F348" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G348" s="2">
-        <v>33</v>
-      </c>
-      <c r="H348" s="2">
-        <v>8</v>
-      </c>
-      <c r="I348" s="2">
-        <v>25</v>
-      </c>
-      <c r="J348" s="4">
-        <v>0.95</v>
-      </c>
-      <c r="K348" s="4">
-        <v>8.6602540378443851E-2</v>
-      </c>
-      <c r="L348" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="M348" s="4">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="N348" s="4">
-        <v>1</v>
-      </c>
-      <c r="O348" s="4">
-        <v>0</v>
-      </c>
-      <c r="P348" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q348" s="4">
-        <v>0</v>
-      </c>
-      <c r="R348" s="4">
-        <v>1</v>
-      </c>
-      <c r="S348" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="349" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A349" s="2">
-        <v>10</v>
-      </c>
-      <c r="B349" s="2">
-        <v>10</v>
-      </c>
-      <c r="C349" s="2">
-        <v>0</v>
-      </c>
-      <c r="D349" s="2">
-        <v>5</v>
-      </c>
-      <c r="E349" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F349" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G349" s="2">
-        <v>33</v>
-      </c>
-      <c r="H349" s="2">
-        <v>8</v>
-      </c>
-      <c r="I349" s="2">
-        <v>25</v>
-      </c>
-      <c r="J349" s="4">
-        <v>0.95</v>
-      </c>
-      <c r="K349" s="4">
-        <v>8.6602540378443851E-2</v>
-      </c>
-      <c r="L349" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="M349" s="4">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="N349" s="4">
-        <v>1</v>
-      </c>
-      <c r="O349" s="4">
-        <v>0</v>
-      </c>
-      <c r="P349" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q349" s="4">
-        <v>0</v>
-      </c>
-      <c r="R349" s="4">
-        <v>1</v>
-      </c>
-      <c r="S349" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A350" s="2">
-        <v>10</v>
-      </c>
-      <c r="B350" s="2">
-        <v>10</v>
-      </c>
-      <c r="C350" s="2">
-        <v>0</v>
-      </c>
-      <c r="D350" s="2">
-        <v>5</v>
-      </c>
-      <c r="E350" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F350" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G350" s="2">
-        <v>33</v>
-      </c>
-      <c r="H350" s="2">
-        <v>8</v>
-      </c>
-      <c r="I350" s="2">
-        <v>25</v>
-      </c>
-      <c r="J350" s="4">
-        <v>0.8666666666666667</v>
-      </c>
-      <c r="K350" s="4">
-        <v>0.1414213562373095</v>
-      </c>
-      <c r="L350" s="4">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="M350" s="4">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="N350" s="4">
-        <v>1</v>
-      </c>
-      <c r="O350" s="4">
-        <v>0</v>
-      </c>
-      <c r="P350" s="4">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="Q350" s="4">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="R350" s="4">
-        <v>0.94791666666666674</v>
-      </c>
-      <c r="S350" s="4">
-        <v>5.4126587736527412E-2</v>
-      </c>
-    </row>
-    <row r="351" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A351" s="2">
-        <v>10</v>
-      </c>
-      <c r="B351" s="2">
-        <v>10</v>
-      </c>
-      <c r="C351" s="2">
-        <v>0</v>
-      </c>
-      <c r="D351" s="2">
-        <v>5</v>
-      </c>
-      <c r="E351" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F351" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G351" s="2">
-        <v>33</v>
-      </c>
-      <c r="H351" s="2">
-        <v>8</v>
-      </c>
-      <c r="I351" s="2">
-        <v>25</v>
-      </c>
-      <c r="J351" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="K351" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="L351" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="M351" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="N351" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="O351" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="P351" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q351" s="4">
-        <v>0</v>
-      </c>
-      <c r="R351" s="4">
-        <v>1</v>
-      </c>
-      <c r="S351" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="352" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A352" s="2">
-        <v>10</v>
-      </c>
-      <c r="B352" s="2">
-        <v>10</v>
-      </c>
-      <c r="C352" s="2">
-        <v>0</v>
-      </c>
-      <c r="D352" s="2">
-        <v>5</v>
-      </c>
-      <c r="E352" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F352" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G352" s="2">
-        <v>33</v>
-      </c>
-      <c r="H352" s="2">
-        <v>8</v>
-      </c>
-      <c r="I352" s="2">
-        <v>25</v>
-      </c>
-      <c r="J352" s="4">
-        <v>0</v>
-      </c>
-      <c r="K352" s="4">
-        <v>0</v>
-      </c>
-      <c r="L352" s="4">
-        <v>0</v>
-      </c>
-      <c r="M352" s="4">
-        <v>0</v>
-      </c>
-      <c r="N352" s="4">
-        <v>0</v>
-      </c>
-      <c r="O352" s="4">
-        <v>0</v>
-      </c>
-      <c r="P352" s="4">
-        <v>0.29761904761904762</v>
-      </c>
-      <c r="Q352" s="4">
-        <v>0.10309826235529029</v>
-      </c>
-      <c r="R352" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="S352" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="353" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A353" s="2">
-        <v>10</v>
-      </c>
-      <c r="B353" s="2">
-        <v>10</v>
-      </c>
-      <c r="C353" s="2">
-        <v>0</v>
-      </c>
-      <c r="D353" s="2">
-        <v>5</v>
-      </c>
-      <c r="E353" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F353" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G353" s="2">
-        <v>33</v>
-      </c>
-      <c r="H353" s="2">
-        <v>8</v>
-      </c>
-      <c r="I353" s="2">
-        <v>25</v>
-      </c>
-      <c r="J353" s="4">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="K353" s="4">
-        <v>0.19245008972987529</v>
-      </c>
-      <c r="L353" s="4">
-        <v>7.1428571428571425E-2</v>
-      </c>
-      <c r="M353" s="4">
-        <v>0.1237179148263484</v>
-      </c>
-      <c r="N353" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="O353" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="P353" s="4">
-        <v>0.29761904761904762</v>
-      </c>
-      <c r="Q353" s="4">
-        <v>0.10309826235529029</v>
-      </c>
-      <c r="R353" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="S353" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="354" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A354" s="2">
-        <v>10</v>
-      </c>
-      <c r="B354" s="2">
-        <v>10</v>
-      </c>
-      <c r="C354" s="2">
-        <v>0</v>
-      </c>
-      <c r="D354" s="2">
-        <v>5</v>
-      </c>
-      <c r="E354" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F354" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G354" s="2">
-        <v>33</v>
-      </c>
-      <c r="H354" s="2">
-        <v>8</v>
-      </c>
-      <c r="I354" s="2">
-        <v>25</v>
-      </c>
-      <c r="J354" s="4">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="K354" s="4">
-        <v>0.19245008972987529</v>
-      </c>
-      <c r="L354" s="4">
-        <v>7.1428571428571425E-2</v>
-      </c>
-      <c r="M354" s="4">
-        <v>0.1237179148263484</v>
-      </c>
-      <c r="N354" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="O354" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="P354" s="4">
-        <v>0.29761904761904762</v>
-      </c>
-      <c r="Q354" s="4">
-        <v>0.10309826235529029</v>
-      </c>
-      <c r="R354" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="S354" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="355" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A355" s="2">
-        <v>10</v>
-      </c>
-      <c r="B355" s="2">
-        <v>10</v>
-      </c>
-      <c r="C355" s="2">
-        <v>0</v>
-      </c>
-      <c r="D355" s="2">
-        <v>5</v>
-      </c>
-      <c r="E355" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F355" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G355" s="2">
-        <v>33</v>
-      </c>
-      <c r="H355" s="2">
-        <v>8</v>
-      </c>
-      <c r="I355" s="2">
-        <v>25</v>
-      </c>
-      <c r="J355" s="4">
-        <v>0.2361111111111111</v>
-      </c>
-      <c r="K355" s="4">
-        <v>0.2369266959615553</v>
-      </c>
-      <c r="L355" s="4">
-        <v>0.15476190476190479</v>
-      </c>
-      <c r="M355" s="4">
-        <v>0.1556749622693098</v>
-      </c>
-      <c r="N355" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="O355" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="P355" s="4">
-        <v>0.29761904761904762</v>
-      </c>
-      <c r="Q355" s="4">
-        <v>0.10309826235529029</v>
-      </c>
-      <c r="R355" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="S355" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A356" s="2">
-        <v>10</v>
-      </c>
-      <c r="B356" s="2">
-        <v>10</v>
-      </c>
-      <c r="C356" s="2">
-        <v>0</v>
-      </c>
-      <c r="D356" s="2">
-        <v>5</v>
-      </c>
-      <c r="E356" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F356" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G356" s="2">
-        <v>33</v>
-      </c>
-      <c r="H356" s="2">
-        <v>8</v>
-      </c>
-      <c r="I356" s="2">
-        <v>25</v>
-      </c>
-      <c r="J356" s="4">
-        <v>0</v>
-      </c>
-      <c r="K356" s="4">
-        <v>0</v>
-      </c>
-      <c r="L356" s="4">
-        <v>0</v>
-      </c>
-      <c r="M356" s="4">
-        <v>0</v>
-      </c>
-      <c r="N356" s="4">
-        <v>0</v>
-      </c>
-      <c r="O356" s="4">
-        <v>0</v>
-      </c>
-      <c r="P356" s="4">
-        <v>0.29761904761904762</v>
-      </c>
-      <c r="Q356" s="4">
-        <v>0.10309826235529029</v>
-      </c>
-      <c r="R356" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="S356" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A357" s="2">
-        <v>10</v>
-      </c>
-      <c r="B357" s="2">
-        <v>10</v>
-      </c>
-      <c r="C357" s="2">
-        <v>0</v>
-      </c>
-      <c r="D357" s="2">
-        <v>5</v>
-      </c>
-      <c r="E357" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F357" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G357" s="2">
-        <v>33</v>
-      </c>
-      <c r="H357" s="2">
-        <v>8</v>
-      </c>
-      <c r="I357" s="2">
-        <v>25</v>
-      </c>
-      <c r="J357" s="4">
-        <v>0</v>
-      </c>
-      <c r="K357" s="4">
-        <v>0</v>
-      </c>
-      <c r="L357" s="4">
-        <v>0</v>
-      </c>
-      <c r="M357" s="4">
-        <v>0</v>
-      </c>
-      <c r="N357" s="4">
-        <v>0</v>
-      </c>
-      <c r="O357" s="4">
-        <v>0</v>
-      </c>
-      <c r="P357" s="4">
-        <v>0.78472222222222221</v>
-      </c>
-      <c r="Q357" s="4">
-        <v>0.1804219591217581</v>
-      </c>
-      <c r="R357" s="4">
-        <v>0.83958333333333335</v>
-      </c>
-      <c r="S357" s="4">
-        <v>0.13735788109897451</v>
-      </c>
-    </row>
-    <row r="358" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A358" s="2">
-        <v>10</v>
-      </c>
-      <c r="B358" s="2">
-        <v>10</v>
-      </c>
-      <c r="C358" s="2">
-        <v>0</v>
-      </c>
-      <c r="D358" s="2">
-        <v>5</v>
-      </c>
-      <c r="E358" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F358" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G358" s="2">
-        <v>33</v>
-      </c>
-      <c r="H358" s="2">
-        <v>8</v>
-      </c>
-      <c r="I358" s="2">
-        <v>25</v>
-      </c>
-      <c r="J358" s="4">
-        <v>0.16666666666666671</v>
-      </c>
-      <c r="K358" s="4">
-        <v>0.28867513459481292</v>
-      </c>
-      <c r="L358" s="4">
-        <v>0.125</v>
-      </c>
-      <c r="M358" s="4">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="N358" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="O358" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="P358" s="4">
-        <v>0.46418650793650801</v>
-      </c>
-      <c r="Q358" s="4">
-        <v>0.19461653685934091</v>
-      </c>
-      <c r="R358" s="4">
-        <v>0.53749999999999998</v>
-      </c>
-      <c r="S358" s="4">
-        <v>0.12930100540985751</v>
-      </c>
-    </row>
-    <row r="359" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A359" s="2">
-        <v>10</v>
-      </c>
-      <c r="B359" s="2">
-        <v>10</v>
-      </c>
-      <c r="C359" s="2">
-        <v>0</v>
-      </c>
-      <c r="D359" s="2">
-        <v>5</v>
-      </c>
-      <c r="E359" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F359" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G359" s="2">
-        <v>33</v>
-      </c>
-      <c r="H359" s="2">
-        <v>8</v>
-      </c>
-      <c r="I359" s="2">
-        <v>25</v>
-      </c>
-      <c r="J359" s="4">
-        <v>0.16666666666666671</v>
-      </c>
-      <c r="K359" s="4">
-        <v>0.28867513459481292</v>
-      </c>
-      <c r="L359" s="4">
-        <v>0.125</v>
-      </c>
-      <c r="M359" s="4">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="N359" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="O359" s="4">
-        <v>0.4330127018922193</v>
-      </c>
-      <c r="P359" s="4">
-        <v>0.36001984126984121</v>
-      </c>
-      <c r="Q359" s="4">
-        <v>0.12547634578015149</v>
-      </c>
-      <c r="R359" s="4">
-        <v>0.40833333333333333</v>
-      </c>
-      <c r="S359" s="4">
-        <v>9.2421137553411803E-2</v>
-      </c>
-    </row>
-    <row r="360" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A360" s="2">
-        <v>10</v>
-      </c>
-      <c r="B360" s="2">
-        <v>10</v>
-      </c>
-      <c r="C360" s="2">
-        <v>0</v>
-      </c>
-      <c r="D360" s="2">
-        <v>5</v>
-      </c>
-      <c r="E360" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F360" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G360" s="2">
-        <v>33</v>
-      </c>
-      <c r="H360" s="2">
-        <v>8</v>
-      </c>
-      <c r="I360" s="2">
-        <v>25</v>
-      </c>
-      <c r="J360" s="4">
-        <v>0.63452380952380949</v>
-      </c>
-      <c r="K360" s="4">
-        <v>0.11235345708845761</v>
-      </c>
-      <c r="L360" s="4">
-        <v>0.51666666666666661</v>
-      </c>
-      <c r="M360" s="4">
-        <v>0.15184055965240489</v>
-      </c>
-      <c r="N360" s="4">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="O360" s="4">
-        <v>0.14433756729740649</v>
-      </c>
-      <c r="P360" s="4">
-        <v>0.49682539682539678</v>
-      </c>
-      <c r="Q360" s="4">
-        <v>0.13521909099648929</v>
-      </c>
-      <c r="R360" s="4">
-        <v>0.76666666666666672</v>
-      </c>
-      <c r="S360" s="4">
-        <v>0.1068812944865055</v>
-      </c>
-    </row>
-    <row r="361" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A361" s="2">
-        <v>10</v>
-      </c>
-      <c r="B361" s="2">
-        <v>10</v>
-      </c>
-      <c r="C361" s="2">
-        <v>0</v>
-      </c>
-      <c r="D361" s="2">
-        <v>5</v>
-      </c>
-      <c r="E361" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F361" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G361" s="2">
-        <v>33</v>
-      </c>
-      <c r="H361" s="2">
-        <v>8</v>
-      </c>
-      <c r="I361" s="2">
-        <v>25</v>
-      </c>
-      <c r="J361" s="4">
-        <v>0.26666666666666672</v>
-      </c>
-      <c r="K361" s="4">
-        <v>0.28284271247461901</v>
-      </c>
-      <c r="L361" s="4">
-        <v>0.375</v>
-      </c>
-      <c r="M361" s="4">
-        <v>0.41457809879442498</v>
-      </c>
-      <c r="N361" s="4">
-        <v>0.20833333333333329</v>
-      </c>
-      <c r="O361" s="4">
-        <v>0.21650635094610959</v>
-      </c>
-      <c r="P361" s="4">
-        <v>0.57291666666666663</v>
-      </c>
-      <c r="Q361" s="4">
-        <v>0.27609472760469572</v>
-      </c>
-      <c r="R361" s="4">
-        <v>0.61458333333333326</v>
-      </c>
-      <c r="S361" s="4">
-        <v>0.26902440771135328</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:S289" xr:uid="{00000000-0001-0000-0300-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S289">
-      <sortCondition ref="A2:A289"/>
-      <sortCondition ref="F2:F289"/>
-      <sortCondition ref="E2:E289"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:S289" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>